--- a/research/traditional_assets/database/data/bulgaria/bulgaria_oil_gas_production_and_exploration.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_oil_gas_production_and_exploration.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1079744267190534</v>
+        <v>0.1079069522923344</v>
       </c>
       <c r="C2">
-        <v>23.22294637822533</v>
+        <v>23.00184094916195</v>
       </c>
       <c r="D2">
-        <v>19.68294637822533</v>
+        <v>19.69378094916195</v>
       </c>
       <c r="E2">
-        <v>-0.294</v>
+        <v>-0.06205999999999998</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.23194</v>
       </c>
       <c r="G2">
         <v>3.54</v>
@@ -1445,28 +1445,28 @@
         <v>1.685</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.011666582</v>
       </c>
       <c r="N2">
-        <v>1.685</v>
+        <v>1.673333418</v>
       </c>
       <c r="O2">
-        <v>0.1685</v>
+        <v>0.1673333418</v>
       </c>
       <c r="P2">
-        <v>1.5165</v>
+        <v>1.5060000762</v>
       </c>
       <c r="Q2">
-        <v>4.0065</v>
+        <v>3.9960000762</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1079744267190534</v>
+        <v>0.1085396487801357</v>
       </c>
       <c r="T2">
-        <v>0.9618186075065634</v>
+        <v>0.9705624130293503</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>144.4296195749534</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1079069522923344</v>
+        <v>0.1078394778656153</v>
       </c>
       <c r="C3">
-        <v>23.00184094916195</v>
+        <v>22.78074745454958</v>
       </c>
       <c r="D3">
-        <v>19.69378094916195</v>
+        <v>19.70462745454958</v>
       </c>
       <c r="E3">
-        <v>-0.06205999999999998</v>
+        <v>0.16988</v>
       </c>
       <c r="F3">
-        <v>0.23194</v>
+        <v>0.46388</v>
       </c>
       <c r="G3">
         <v>3.54</v>
@@ -1527,28 +1527,28 @@
         <v>1.685</v>
       </c>
       <c r="M3">
-        <v>0.011666582</v>
+        <v>0.023333164</v>
       </c>
       <c r="N3">
-        <v>1.673333418</v>
+        <v>1.661666836</v>
       </c>
       <c r="O3">
-        <v>0.1673333418</v>
+        <v>0.1661666836</v>
       </c>
       <c r="P3">
-        <v>1.5060000762</v>
+        <v>1.4955001524</v>
       </c>
       <c r="Q3">
-        <v>3.9960000762</v>
+        <v>3.9855001524</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1085396487801357</v>
+        <v>0.1091164059853217</v>
       </c>
       <c r="T3">
-        <v>0.9705624130293503</v>
+        <v>0.9794846635628065</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>144.4296195749534</v>
+        <v>72.21480978747672</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1078394778656153</v>
+        <v>0.1077720034388962</v>
       </c>
       <c r="C4">
-        <v>22.78074745454958</v>
+        <v>22.55966591411807</v>
       </c>
       <c r="D4">
-        <v>19.70462745454958</v>
+        <v>19.71548591411807</v>
       </c>
       <c r="E4">
-        <v>0.16988</v>
+        <v>0.40182</v>
       </c>
       <c r="F4">
-        <v>0.46388</v>
+        <v>0.69582</v>
       </c>
       <c r="G4">
         <v>3.54</v>
@@ -1609,28 +1609,28 @@
         <v>1.685</v>
       </c>
       <c r="M4">
-        <v>0.023333164</v>
+        <v>0.034999746</v>
       </c>
       <c r="N4">
-        <v>1.661666836</v>
+        <v>1.650000254</v>
       </c>
       <c r="O4">
-        <v>0.1661666836</v>
+        <v>0.1650000254</v>
       </c>
       <c r="P4">
-        <v>1.4955001524</v>
+        <v>1.4850002286</v>
       </c>
       <c r="Q4">
-        <v>3.9855001524</v>
+        <v>3.9750002286</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1091164059853217</v>
+        <v>0.1097050550916456</v>
       </c>
       <c r="T4">
-        <v>0.9794846635628065</v>
+        <v>0.9885908780247873</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>72.21480978747672</v>
+        <v>48.14320652498449</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1077720034388962</v>
+        <v>0.1077045290121772</v>
       </c>
       <c r="C5">
-        <v>22.55966591411807</v>
+        <v>22.33859634764078</v>
       </c>
       <c r="D5">
-        <v>19.71548591411807</v>
+        <v>19.72635634764078</v>
       </c>
       <c r="E5">
-        <v>0.40182</v>
+        <v>0.6337600000000001</v>
       </c>
       <c r="F5">
-        <v>0.69582</v>
+        <v>0.92776</v>
       </c>
       <c r="G5">
         <v>3.54</v>
@@ -1691,28 +1691,28 @@
         <v>1.685</v>
       </c>
       <c r="M5">
-        <v>0.034999746</v>
+        <v>0.046666328</v>
       </c>
       <c r="N5">
-        <v>1.650000254</v>
+        <v>1.638333672</v>
       </c>
       <c r="O5">
-        <v>0.1650000254</v>
+        <v>0.1638333672</v>
       </c>
       <c r="P5">
-        <v>1.4850002286</v>
+        <v>1.4745003048</v>
       </c>
       <c r="Q5">
-        <v>3.9750002286</v>
+        <v>3.9645003048</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1097050550916456</v>
+        <v>0.1103059677210179</v>
       </c>
       <c r="T5">
-        <v>0.9885908780247873</v>
+        <v>0.9978868052880596</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.14320652498449</v>
+        <v>36.10740489373836</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1077045290121772</v>
+        <v>0.1076370545854581</v>
       </c>
       <c r="C6">
-        <v>22.33859634764078</v>
+        <v>22.11753877493471</v>
       </c>
       <c r="D6">
-        <v>19.72635634764078</v>
+        <v>19.73723877493471</v>
       </c>
       <c r="E6">
-        <v>0.6337600000000001</v>
+        <v>0.8656999999999999</v>
       </c>
       <c r="F6">
-        <v>0.92776</v>
+        <v>1.1597</v>
       </c>
       <c r="G6">
         <v>3.54</v>
@@ -1773,28 +1773,28 @@
         <v>1.685</v>
       </c>
       <c r="M6">
-        <v>0.046666328</v>
+        <v>0.05833290999999999</v>
       </c>
       <c r="N6">
-        <v>1.638333672</v>
+        <v>1.62666709</v>
       </c>
       <c r="O6">
-        <v>0.1638333672</v>
+        <v>0.162666709</v>
       </c>
       <c r="P6">
-        <v>1.4745003048</v>
+        <v>1.464000381</v>
       </c>
       <c r="Q6">
-        <v>3.9645003048</v>
+        <v>3.954000381</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1103059677210179</v>
+        <v>0.1109195311425875</v>
       </c>
       <c r="T6">
-        <v>0.9978868052880596</v>
+        <v>1.00737843628319</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.10740489373836</v>
+        <v>28.88592391499069</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1076370545854581</v>
+        <v>0.1075695801587391</v>
       </c>
       <c r="C7">
-        <v>22.11753877493471</v>
+        <v>21.8964932158606</v>
       </c>
       <c r="D7">
-        <v>19.73723877493471</v>
+        <v>19.7481332158606</v>
       </c>
       <c r="E7">
-        <v>0.8656999999999999</v>
+        <v>1.09764</v>
       </c>
       <c r="F7">
-        <v>1.1597</v>
+        <v>1.39164</v>
       </c>
       <c r="G7">
         <v>3.54</v>
@@ -1855,28 +1855,28 @@
         <v>1.685</v>
       </c>
       <c r="M7">
-        <v>0.05833290999999999</v>
+        <v>0.069999492</v>
       </c>
       <c r="N7">
-        <v>1.62666709</v>
+        <v>1.615000508</v>
       </c>
       <c r="O7">
-        <v>0.162666709</v>
+        <v>0.1615000508</v>
       </c>
       <c r="P7">
-        <v>1.464000381</v>
+        <v>1.4535004572</v>
       </c>
       <c r="Q7">
-        <v>3.954000381</v>
+        <v>3.9435004572</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1109195311425875</v>
+        <v>0.1115461491050416</v>
       </c>
       <c r="T7">
-        <v>1.00737843628319</v>
+        <v>1.017072016873962</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.88592391499069</v>
+        <v>24.07160326249224</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1075695801587391</v>
+        <v>0.10750210573202</v>
       </c>
       <c r="C8">
-        <v>21.8964932158606</v>
+        <v>21.67545969032307</v>
       </c>
       <c r="D8">
-        <v>19.7481332158606</v>
+        <v>19.75903969032307</v>
       </c>
       <c r="E8">
-        <v>1.09764</v>
+        <v>1.32958</v>
       </c>
       <c r="F8">
-        <v>1.39164</v>
+        <v>1.62358</v>
       </c>
       <c r="G8">
         <v>3.54</v>
@@ -1937,28 +1937,28 @@
         <v>1.685</v>
       </c>
       <c r="M8">
-        <v>0.069999492</v>
+        <v>0.08166607399999999</v>
       </c>
       <c r="N8">
-        <v>1.615000508</v>
+        <v>1.603333926</v>
       </c>
       <c r="O8">
-        <v>0.1615000508</v>
+        <v>0.1603333926</v>
       </c>
       <c r="P8">
-        <v>1.4535004572</v>
+        <v>1.4430005334</v>
       </c>
       <c r="Q8">
-        <v>3.9435004572</v>
+        <v>3.9330005334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1115461491050416</v>
+        <v>0.1121862427226022</v>
       </c>
       <c r="T8">
-        <v>1.017072016873962</v>
+        <v>1.026974061563459</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.07160326249224</v>
+        <v>20.63280279642192</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.10750210573202</v>
+        <v>0.107434631305301</v>
       </c>
       <c r="C9">
-        <v>21.67545969032307</v>
+        <v>21.45443821827075</v>
       </c>
       <c r="D9">
-        <v>19.75903969032307</v>
+        <v>19.76995821827074</v>
       </c>
       <c r="E9">
-        <v>1.32958</v>
+        <v>1.56152</v>
       </c>
       <c r="F9">
-        <v>1.62358</v>
+        <v>1.85552</v>
       </c>
       <c r="G9">
         <v>3.54</v>
@@ -2019,28 +2019,28 @@
         <v>1.685</v>
       </c>
       <c r="M9">
-        <v>0.08166607399999999</v>
+        <v>0.093332656</v>
       </c>
       <c r="N9">
-        <v>1.603333926</v>
+        <v>1.591667344</v>
       </c>
       <c r="O9">
-        <v>0.1603333926</v>
+        <v>0.1591667344</v>
       </c>
       <c r="P9">
-        <v>1.4430005334</v>
+        <v>1.432500609599999</v>
       </c>
       <c r="Q9">
-        <v>3.9330005334</v>
+        <v>3.9225006096</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1121862427226022</v>
+        <v>0.1128402514188054</v>
       </c>
       <c r="T9">
-        <v>1.02697406156346</v>
+        <v>1.037091368094034</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.63280279642192</v>
+        <v>18.05370244686918</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.107434631305301</v>
+        <v>0.1073671568785819</v>
       </c>
       <c r="C10">
-        <v>21.45443821827075</v>
+        <v>21.23342881969634</v>
       </c>
       <c r="D10">
-        <v>19.76995821827074</v>
+        <v>19.78088881969634</v>
       </c>
       <c r="E10">
-        <v>1.56152</v>
+        <v>1.79346</v>
       </c>
       <c r="F10">
-        <v>1.85552</v>
+        <v>2.08746</v>
       </c>
       <c r="G10">
         <v>3.54</v>
@@ -2101,28 +2101,28 @@
         <v>1.685</v>
       </c>
       <c r="M10">
-        <v>0.093332656</v>
+        <v>0.104999238</v>
       </c>
       <c r="N10">
-        <v>1.591667344</v>
+        <v>1.580000762</v>
       </c>
       <c r="O10">
-        <v>0.1591667344</v>
+        <v>0.1580000762</v>
       </c>
       <c r="P10">
-        <v>1.432500609599999</v>
+        <v>1.4220006858</v>
       </c>
       <c r="Q10">
-        <v>3.9225006096</v>
+        <v>3.9120006858</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1128402514188054</v>
+        <v>0.1135086339325076</v>
       </c>
       <c r="T10">
-        <v>1.037091368094034</v>
+        <v>1.047431033009895</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.05370244686918</v>
+        <v>16.04773550832817</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1073671568785819</v>
+        <v>0.1072996824518629</v>
       </c>
       <c r="C11">
-        <v>21.23342881969634</v>
+        <v>21.01243151463685</v>
       </c>
       <c r="D11">
-        <v>19.78088881969634</v>
+        <v>19.79183151463685</v>
       </c>
       <c r="E11">
-        <v>1.79346</v>
+        <v>2.0254</v>
       </c>
       <c r="F11">
-        <v>2.08746</v>
+        <v>2.3194</v>
       </c>
       <c r="G11">
         <v>3.54</v>
@@ -2183,28 +2183,28 @@
         <v>1.685</v>
       </c>
       <c r="M11">
-        <v>0.104999238</v>
+        <v>0.11666582</v>
       </c>
       <c r="N11">
-        <v>1.580000762</v>
+        <v>1.56833418</v>
       </c>
       <c r="O11">
-        <v>0.1580000762</v>
+        <v>0.156833418</v>
       </c>
       <c r="P11">
-        <v>1.4220006858</v>
+        <v>1.411500762</v>
       </c>
       <c r="Q11">
-        <v>3.9120006858</v>
+        <v>3.901500762</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1135086339325076</v>
+        <v>0.1141918693909588</v>
       </c>
       <c r="T11">
-        <v>1.047431033009895</v>
+        <v>1.05800046825722</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.04773550832817</v>
+        <v>14.44296195749535</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1072996824518629</v>
+        <v>0.1072322080251438</v>
       </c>
       <c r="C12">
-        <v>21.01243151463685</v>
+        <v>20.79144632317362</v>
       </c>
       <c r="D12">
-        <v>19.79183151463685</v>
+        <v>19.80278632317362</v>
       </c>
       <c r="E12">
-        <v>2.0254</v>
+        <v>2.25734</v>
       </c>
       <c r="F12">
-        <v>2.3194</v>
+        <v>2.55134</v>
       </c>
       <c r="G12">
         <v>3.54</v>
@@ -2265,28 +2265,28 @@
         <v>1.685</v>
       </c>
       <c r="M12">
-        <v>0.11666582</v>
+        <v>0.128332402</v>
       </c>
       <c r="N12">
-        <v>1.56833418</v>
+        <v>1.556667598</v>
       </c>
       <c r="O12">
-        <v>0.156833418</v>
+        <v>0.1556667598</v>
       </c>
       <c r="P12">
-        <v>1.411500762</v>
+        <v>1.4010008382</v>
       </c>
       <c r="Q12">
-        <v>3.901500762</v>
+        <v>3.8910008382</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1141918693909588</v>
+        <v>0.1148904584552178</v>
       </c>
       <c r="T12">
-        <v>1.05800046825722</v>
+        <v>1.068807418903361</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.44296195749535</v>
+        <v>13.12996541590486</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1072322080251438</v>
+        <v>0.1073267335984248</v>
       </c>
       <c r="C13">
-        <v>20.79144632317362</v>
+        <v>20.54416302939986</v>
       </c>
       <c r="D13">
-        <v>19.80278632317362</v>
+        <v>19.78744302939986</v>
       </c>
       <c r="E13">
-        <v>2.25734</v>
+        <v>2.48928</v>
       </c>
       <c r="F13">
-        <v>2.55134</v>
+        <v>2.78328</v>
       </c>
       <c r="G13">
         <v>3.54</v>
@@ -2347,45 +2347,45 @@
         <v>1.685</v>
       </c>
       <c r="M13">
-        <v>0.128332402</v>
+        <v>0.144173904</v>
       </c>
       <c r="N13">
-        <v>1.556667598</v>
+        <v>1.540826096</v>
       </c>
       <c r="O13">
-        <v>0.1556667598</v>
+        <v>0.1540826096</v>
       </c>
       <c r="P13">
-        <v>1.4010008382</v>
+        <v>1.386743486399999</v>
       </c>
       <c r="Q13">
-        <v>3.8910008382</v>
+        <v>3.8767434864</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1148904584552178</v>
+        <v>0.1156049245436645</v>
       </c>
       <c r="T13">
-        <v>1.068807418903361</v>
+        <v>1.079859982064187</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.1</v>
       </c>
       <c r="W13">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.12996541590486</v>
+        <v>11.68727455698224</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1073267335984248</v>
+        <v>0.1072727591717057</v>
       </c>
       <c r="C14">
-        <v>20.54416302939986</v>
+        <v>20.32098118942717</v>
       </c>
       <c r="D14">
-        <v>19.78744302939986</v>
+        <v>19.79620118942717</v>
       </c>
       <c r="E14">
-        <v>2.48928</v>
+        <v>2.72122</v>
       </c>
       <c r="F14">
-        <v>2.78328</v>
+        <v>3.01522</v>
       </c>
       <c r="G14">
         <v>3.54</v>
@@ -2429,28 +2429,28 @@
         <v>1.685</v>
       </c>
       <c r="M14">
-        <v>0.144173904</v>
+        <v>0.156188396</v>
       </c>
       <c r="N14">
-        <v>1.540826096</v>
+        <v>1.528811604</v>
       </c>
       <c r="O14">
-        <v>0.1540826096</v>
+        <v>0.1528811604</v>
       </c>
       <c r="P14">
-        <v>1.386743486399999</v>
+        <v>1.3759304436</v>
       </c>
       <c r="Q14">
-        <v>3.8767434864</v>
+        <v>3.8659304436</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1156049245436645</v>
+        <v>0.1163358151398916</v>
       </c>
       <c r="T14">
-        <v>1.079859982064187</v>
+        <v>1.091166627136756</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.68727455698224</v>
+        <v>10.78825343721437</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1072727591717057</v>
+        <v>0.1072187847449867</v>
       </c>
       <c r="C15">
-        <v>20.32098118942717</v>
+        <v>20.09780710582125</v>
       </c>
       <c r="D15">
-        <v>19.79620118942717</v>
+        <v>19.80496710582125</v>
       </c>
       <c r="E15">
-        <v>2.72122</v>
+        <v>2.95316</v>
       </c>
       <c r="F15">
-        <v>3.01522</v>
+        <v>3.24716</v>
       </c>
       <c r="G15">
         <v>3.54</v>
@@ -2511,28 +2511,28 @@
         <v>1.685</v>
       </c>
       <c r="M15">
-        <v>0.156188396</v>
+        <v>0.168202888</v>
       </c>
       <c r="N15">
-        <v>1.528811604</v>
+        <v>1.516797112</v>
       </c>
       <c r="O15">
-        <v>0.1528811604</v>
+        <v>0.1516797112</v>
       </c>
       <c r="P15">
-        <v>1.3759304436</v>
+        <v>1.3651174008</v>
       </c>
       <c r="Q15">
-        <v>3.8659304436</v>
+        <v>3.8551174008</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1163358151398916</v>
+        <v>0.117083703191845</v>
       </c>
       <c r="T15">
-        <v>1.091166627136756</v>
+        <v>1.102736217443572</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.78825343721437</v>
+        <v>10.01766390598478</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1072187847449867</v>
+        <v>0.1073943103182676</v>
       </c>
       <c r="C16">
-        <v>20.09780710582125</v>
+        <v>19.83738861237624</v>
       </c>
       <c r="D16">
-        <v>19.80496710582125</v>
+        <v>19.77648861237624</v>
       </c>
       <c r="E16">
-        <v>2.95316</v>
+        <v>3.1851</v>
       </c>
       <c r="F16">
-        <v>3.24716</v>
+        <v>3.4791</v>
       </c>
       <c r="G16">
         <v>3.54</v>
@@ -2593,45 +2593,45 @@
         <v>1.685</v>
       </c>
       <c r="M16">
-        <v>0.168202888</v>
+        <v>0.18613185</v>
       </c>
       <c r="N16">
-        <v>1.516797112</v>
+        <v>1.49886815</v>
       </c>
       <c r="O16">
-        <v>0.1516797112</v>
+        <v>0.149886815</v>
       </c>
       <c r="P16">
-        <v>1.3651174008</v>
+        <v>1.348981335</v>
       </c>
       <c r="Q16">
-        <v>3.8551174008</v>
+        <v>3.838981335</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.117083703191845</v>
+        <v>0.1178491886097266</v>
       </c>
       <c r="T16">
-        <v>1.102736217443572</v>
+        <v>1.114578033404665</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.1</v>
       </c>
       <c r="W16">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.01766390598478</v>
+        <v>9.0527225727354</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1073943103182676</v>
+        <v>0.1073556358915486</v>
       </c>
       <c r="C17">
-        <v>19.83738861237624</v>
+        <v>19.6117163841291</v>
       </c>
       <c r="D17">
-        <v>19.77648861237624</v>
+        <v>19.7827563841291</v>
       </c>
       <c r="E17">
-        <v>3.1851</v>
+        <v>3.41704</v>
       </c>
       <c r="F17">
-        <v>3.4791</v>
+        <v>3.71104</v>
       </c>
       <c r="G17">
         <v>3.54</v>
@@ -2675,28 +2675,28 @@
         <v>1.685</v>
       </c>
       <c r="M17">
-        <v>0.18613185</v>
+        <v>0.19854064</v>
       </c>
       <c r="N17">
-        <v>1.49886815</v>
+        <v>1.48645936</v>
       </c>
       <c r="O17">
-        <v>0.149886815</v>
+        <v>0.148645936</v>
       </c>
       <c r="P17">
-        <v>1.348981335</v>
+        <v>1.337813424</v>
       </c>
       <c r="Q17">
-        <v>3.838981335</v>
+        <v>3.827813424</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1178491886097266</v>
+        <v>0.1186328998708912</v>
       </c>
       <c r="T17">
-        <v>1.114578033404665</v>
+        <v>1.126701797364831</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.052722572735401</v>
+        <v>8.486927411939437</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1073556358915486</v>
+        <v>0.1073169614648295</v>
       </c>
       <c r="C18">
-        <v>19.6117163841291</v>
+        <v>19.38604813003713</v>
       </c>
       <c r="D18">
-        <v>19.7827563841291</v>
+        <v>19.78902813003713</v>
       </c>
       <c r="E18">
-        <v>3.41704</v>
+        <v>3.64898</v>
       </c>
       <c r="F18">
-        <v>3.71104</v>
+        <v>3.94298</v>
       </c>
       <c r="G18">
         <v>3.54</v>
@@ -2757,28 +2757,28 @@
         <v>1.685</v>
       </c>
       <c r="M18">
-        <v>0.19854064</v>
+        <v>0.21094943</v>
       </c>
       <c r="N18">
-        <v>1.48645936</v>
+        <v>1.47405057</v>
       </c>
       <c r="O18">
-        <v>0.148645936</v>
+        <v>0.147405057</v>
       </c>
       <c r="P18">
-        <v>1.337813424</v>
+        <v>1.326645513</v>
       </c>
       <c r="Q18">
-        <v>3.827813424</v>
+        <v>3.816645513</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1186328998708912</v>
+        <v>0.1194354957407585</v>
       </c>
       <c r="T18">
-        <v>1.126701797364831</v>
+        <v>1.139117700215605</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.486927411939437</v>
+        <v>7.987696387707707</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1073169614648295</v>
+        <v>0.1074078870381104</v>
       </c>
       <c r="C19">
-        <v>19.38604813003713</v>
+        <v>19.13936924274557</v>
       </c>
       <c r="D19">
-        <v>19.78902813003713</v>
+        <v>19.77428924274557</v>
       </c>
       <c r="E19">
-        <v>3.64898</v>
+        <v>3.88092</v>
       </c>
       <c r="F19">
-        <v>3.94298</v>
+        <v>4.17492</v>
       </c>
       <c r="G19">
         <v>3.54</v>
@@ -2839,45 +2839,45 @@
         <v>1.685</v>
       </c>
       <c r="M19">
-        <v>0.21094943</v>
+        <v>0.226698156</v>
       </c>
       <c r="N19">
-        <v>1.47405057</v>
+        <v>1.458301844</v>
       </c>
       <c r="O19">
-        <v>0.147405057</v>
+        <v>0.1458301844</v>
       </c>
       <c r="P19">
-        <v>1.326645513</v>
+        <v>1.312471659599999</v>
       </c>
       <c r="Q19">
-        <v>3.816645513</v>
+        <v>3.8024716596</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1194354957407585</v>
+        <v>0.1202576671196469</v>
       </c>
       <c r="T19">
-        <v>1.139117700215605</v>
+        <v>1.151836429965177</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.987696387707707</v>
+        <v>7.432790939861017</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1074078870381105</v>
+        <v>0.1073764126113914</v>
       </c>
       <c r="C20">
-        <v>19.13936924274557</v>
+        <v>18.91252871082935</v>
       </c>
       <c r="D20">
-        <v>19.77428924274557</v>
+        <v>19.77938871082935</v>
       </c>
       <c r="E20">
-        <v>3.880919999999999</v>
+        <v>4.11286</v>
       </c>
       <c r="F20">
-        <v>4.174919999999999</v>
+        <v>4.40686</v>
       </c>
       <c r="G20">
         <v>3.54</v>
@@ -2921,28 +2921,28 @@
         <v>1.685</v>
       </c>
       <c r="M20">
-        <v>0.226698156</v>
+        <v>0.239292498</v>
       </c>
       <c r="N20">
-        <v>1.458301844</v>
+        <v>1.445707502</v>
       </c>
       <c r="O20">
-        <v>0.1458301844</v>
+        <v>0.1445707502</v>
       </c>
       <c r="P20">
-        <v>1.3124716596</v>
+        <v>1.3011367518</v>
       </c>
       <c r="Q20">
-        <v>3.8024716596</v>
+        <v>3.7911367518</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1202576671196469</v>
+        <v>0.1211001390264091</v>
       </c>
       <c r="T20">
-        <v>1.151836429965177</v>
+        <v>1.164869202424616</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.43279093986102</v>
+        <v>7.041591416710438</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1073764126113914</v>
+        <v>0.1073449381846724</v>
       </c>
       <c r="C21">
-        <v>18.91252871082935</v>
+        <v>18.68569080973158</v>
       </c>
       <c r="D21">
-        <v>19.77938871082935</v>
+        <v>19.78449080973158</v>
       </c>
       <c r="E21">
-        <v>4.11286</v>
+        <v>4.3448</v>
       </c>
       <c r="F21">
-        <v>4.40686</v>
+        <v>4.6388</v>
       </c>
       <c r="G21">
         <v>3.54</v>
@@ -3003,28 +3003,28 @@
         <v>1.685</v>
       </c>
       <c r="M21">
-        <v>0.239292498</v>
+        <v>0.25188684</v>
       </c>
       <c r="N21">
-        <v>1.445707502</v>
+        <v>1.43311316</v>
       </c>
       <c r="O21">
-        <v>0.1445707502</v>
+        <v>0.143311316</v>
       </c>
       <c r="P21">
-        <v>1.3011367518</v>
+        <v>1.289801844</v>
       </c>
       <c r="Q21">
-        <v>3.7911367518</v>
+        <v>3.779801844</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1211001390264091</v>
+        <v>0.1219636727308404</v>
       </c>
       <c r="T21">
-        <v>1.164869202424616</v>
+        <v>1.17822779419554</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.041591416710438</v>
+        <v>6.689511845874915</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1073449381846724</v>
+        <v>0.1073134637579533</v>
       </c>
       <c r="C22">
-        <v>18.68569080973158</v>
+        <v>18.45885554148866</v>
       </c>
       <c r="D22">
-        <v>19.78449080973158</v>
+        <v>19.78959554148867</v>
       </c>
       <c r="E22">
-        <v>4.3448</v>
+        <v>4.576740000000001</v>
       </c>
       <c r="F22">
-        <v>4.6388</v>
+        <v>4.870740000000001</v>
       </c>
       <c r="G22">
         <v>3.54</v>
@@ -3085,28 +3085,28 @@
         <v>1.685</v>
       </c>
       <c r="M22">
-        <v>0.25188684</v>
+        <v>0.264481182</v>
       </c>
       <c r="N22">
-        <v>1.43311316</v>
+        <v>1.420518818</v>
       </c>
       <c r="O22">
-        <v>0.143311316</v>
+        <v>0.1420518818</v>
       </c>
       <c r="P22">
-        <v>1.289801844</v>
+        <v>1.2784669362</v>
       </c>
       <c r="Q22">
-        <v>3.779801844</v>
+        <v>3.7684669362</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1219636727308404</v>
+        <v>0.1228490680480421</v>
       </c>
       <c r="T22">
-        <v>1.17822779419554</v>
+        <v>1.191924578163197</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.689511845874915</v>
+        <v>6.370963662738014</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1073134637579533</v>
+        <v>0.1074799893312342</v>
       </c>
       <c r="C23">
-        <v>18.45885554148867</v>
+        <v>18.19993717716174</v>
       </c>
       <c r="D23">
-        <v>19.78959554148867</v>
+        <v>19.76261717716174</v>
       </c>
       <c r="E23">
-        <v>4.57674</v>
+        <v>4.80868</v>
       </c>
       <c r="F23">
-        <v>4.87074</v>
+        <v>5.102679999999999</v>
       </c>
       <c r="G23">
         <v>3.54</v>
@@ -3167,45 +3167,45 @@
         <v>1.685</v>
       </c>
       <c r="M23">
-        <v>0.264481182</v>
+        <v>0.282178204</v>
       </c>
       <c r="N23">
-        <v>1.420518818</v>
+        <v>1.402821796</v>
       </c>
       <c r="O23">
-        <v>0.1420518818</v>
+        <v>0.1402821796</v>
       </c>
       <c r="P23">
-        <v>1.2784669362</v>
+        <v>1.2625396164</v>
       </c>
       <c r="Q23">
-        <v>3.7684669362</v>
+        <v>3.7525396164</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1228490680480421</v>
+        <v>0.1237571658092747</v>
       </c>
       <c r="T23">
-        <v>1.191924578163197</v>
+        <v>1.205972561719768</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.1</v>
       </c>
       <c r="W23">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.370963662738016</v>
+        <v>5.971403801265954</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1074799893312342</v>
+        <v>0.1074575149045152</v>
       </c>
       <c r="C24">
-        <v>18.19993717716174</v>
+        <v>17.97163390458858</v>
       </c>
       <c r="D24">
-        <v>19.76261717716174</v>
+        <v>19.76625390458858</v>
       </c>
       <c r="E24">
-        <v>4.80868</v>
+        <v>5.040620000000001</v>
       </c>
       <c r="F24">
-        <v>5.102679999999999</v>
+        <v>5.33462</v>
       </c>
       <c r="G24">
         <v>3.54</v>
@@ -3249,28 +3249,28 @@
         <v>1.685</v>
       </c>
       <c r="M24">
-        <v>0.282178204</v>
+        <v>0.295004486</v>
       </c>
       <c r="N24">
-        <v>1.402821796</v>
+        <v>1.389995514</v>
       </c>
       <c r="O24">
-        <v>0.1402821796</v>
+        <v>0.1389995513999999</v>
       </c>
       <c r="P24">
-        <v>1.2625396164</v>
+        <v>1.2509959626</v>
       </c>
       <c r="Q24">
-        <v>3.7525396164</v>
+        <v>3.7409959626</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1237571658092747</v>
+        <v>0.1246888505253444</v>
       </c>
       <c r="T24">
-        <v>1.205972561719768</v>
+        <v>1.22038542796612</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.971403801265954</v>
+        <v>5.711777549036999</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1074575149045152</v>
+        <v>0.1074350404777961</v>
       </c>
       <c r="C25">
-        <v>17.97163390458858</v>
+        <v>17.74333197072682</v>
       </c>
       <c r="D25">
-        <v>19.76625390458858</v>
+        <v>19.76989197072682</v>
       </c>
       <c r="E25">
-        <v>5.040620000000001</v>
+        <v>5.27256</v>
       </c>
       <c r="F25">
-        <v>5.33462</v>
+        <v>5.56656</v>
       </c>
       <c r="G25">
         <v>3.54</v>
@@ -3331,28 +3331,28 @@
         <v>1.685</v>
       </c>
       <c r="M25">
-        <v>0.295004486</v>
+        <v>0.307830768</v>
       </c>
       <c r="N25">
-        <v>1.389995514</v>
+        <v>1.377169232</v>
       </c>
       <c r="O25">
-        <v>0.1389995513999999</v>
+        <v>0.1377169232</v>
       </c>
       <c r="P25">
-        <v>1.2509959626</v>
+        <v>1.2394523088</v>
       </c>
       <c r="Q25">
-        <v>3.7409959626</v>
+        <v>3.7294523088</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1246888505253444</v>
+        <v>0.1256450532602581</v>
       </c>
       <c r="T25">
-        <v>1.22038542796612</v>
+        <v>1.235177580166324</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.711777549036999</v>
+        <v>5.473786817827123</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1074350404777961</v>
+        <v>0.1074125660510771</v>
       </c>
       <c r="C26">
-        <v>17.74333197072682</v>
+        <v>17.51503137631581</v>
       </c>
       <c r="D26">
-        <v>19.76989197072682</v>
+        <v>19.77353137631581</v>
       </c>
       <c r="E26">
-        <v>5.27256</v>
+        <v>5.5045</v>
       </c>
       <c r="F26">
-        <v>5.56656</v>
+        <v>5.7985</v>
       </c>
       <c r="G26">
         <v>3.54</v>
@@ -3413,28 +3413,28 @@
         <v>1.685</v>
       </c>
       <c r="M26">
-        <v>0.307830768</v>
+        <v>0.32065705</v>
       </c>
       <c r="N26">
-        <v>1.377169232</v>
+        <v>1.36434295</v>
       </c>
       <c r="O26">
-        <v>0.1377169232</v>
+        <v>0.136434295</v>
       </c>
       <c r="P26">
-        <v>1.2394523088</v>
+        <v>1.227908655</v>
       </c>
       <c r="Q26">
-        <v>3.7294523088</v>
+        <v>3.717908655</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1256450532602581</v>
+        <v>0.1266267547347694</v>
       </c>
       <c r="T26">
-        <v>1.235177580166324</v>
+        <v>1.250364189758532</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.473786817827123</v>
+        <v>5.254835345114039</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1074125660510771</v>
+        <v>0.107390091624358</v>
       </c>
       <c r="C27">
-        <v>17.51503137631581</v>
+        <v>17.2867321220954</v>
       </c>
       <c r="D27">
-        <v>19.77353137631581</v>
+        <v>19.7771721220954</v>
       </c>
       <c r="E27">
-        <v>5.5045</v>
+        <v>5.73644</v>
       </c>
       <c r="F27">
-        <v>5.7985</v>
+        <v>6.03044</v>
       </c>
       <c r="G27">
         <v>3.54</v>
@@ -3495,28 +3495,28 @@
         <v>1.685</v>
       </c>
       <c r="M27">
-        <v>0.32065705</v>
+        <v>0.333483332</v>
       </c>
       <c r="N27">
-        <v>1.36434295</v>
+        <v>1.351516668</v>
       </c>
       <c r="O27">
-        <v>0.136434295</v>
+        <v>0.1351516668</v>
       </c>
       <c r="P27">
-        <v>1.227908655</v>
+        <v>1.2163650012</v>
       </c>
       <c r="Q27">
-        <v>3.717908655</v>
+        <v>3.7063650012</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1266267547347694</v>
+        <v>0.1276349886815649</v>
       </c>
       <c r="T27">
-        <v>1.250364189758532</v>
+        <v>1.265961248258639</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.254835345114039</v>
+        <v>5.052726293378885</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.107390091624358</v>
+        <v>0.107367617197639</v>
       </c>
       <c r="C28">
-        <v>17.2867321220954</v>
+        <v>17.05843420880603</v>
       </c>
       <c r="D28">
-        <v>19.7771721220954</v>
+        <v>19.78081420880603</v>
       </c>
       <c r="E28">
-        <v>5.73644</v>
+        <v>5.968380000000001</v>
       </c>
       <c r="F28">
-        <v>6.03044</v>
+        <v>6.26238</v>
       </c>
       <c r="G28">
         <v>3.54</v>
@@ -3577,28 +3577,28 @@
         <v>1.685</v>
       </c>
       <c r="M28">
-        <v>0.333483332</v>
+        <v>0.346309614</v>
       </c>
       <c r="N28">
-        <v>1.351516668</v>
+        <v>1.338690386</v>
       </c>
       <c r="O28">
-        <v>0.1351516668</v>
+        <v>0.1338690386</v>
       </c>
       <c r="P28">
-        <v>1.2163650012</v>
+        <v>1.2048213474</v>
       </c>
       <c r="Q28">
-        <v>3.7063650012</v>
+        <v>3.6948213474</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1276349886815649</v>
+        <v>0.1286708454762178</v>
       </c>
       <c r="T28">
-        <v>1.265961248258639</v>
+        <v>1.281985623429981</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.052726293378885</v>
+        <v>4.865588282512999</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.107367617197639</v>
+        <v>0.1073451427709199</v>
       </c>
       <c r="C29">
-        <v>17.05843420880603</v>
+        <v>16.83013763718863</v>
       </c>
       <c r="D29">
-        <v>19.78081420880603</v>
+        <v>19.78445763718863</v>
       </c>
       <c r="E29">
-        <v>5.968380000000001</v>
+        <v>6.20032</v>
       </c>
       <c r="F29">
-        <v>6.26238</v>
+        <v>6.49432</v>
       </c>
       <c r="G29">
         <v>3.54</v>
@@ -3659,28 +3659,28 @@
         <v>1.685</v>
       </c>
       <c r="M29">
-        <v>0.346309614</v>
+        <v>0.359135896</v>
       </c>
       <c r="N29">
-        <v>1.338690386</v>
+        <v>1.325864104</v>
       </c>
       <c r="O29">
-        <v>0.1338690386</v>
+        <v>0.1325864104</v>
       </c>
       <c r="P29">
-        <v>1.2048213474</v>
+        <v>1.1932776936</v>
       </c>
       <c r="Q29">
-        <v>3.6948213474</v>
+        <v>3.6832776936</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1286708454762178</v>
+        <v>0.1297354760707221</v>
       </c>
       <c r="T29">
-        <v>1.281985623429981</v>
+        <v>1.298455120133861</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.865588282512999</v>
+        <v>4.691817272423249</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1073451427709199</v>
+        <v>0.1073226683442009</v>
       </c>
       <c r="C30">
-        <v>16.83013763718863</v>
+        <v>16.60184240798472</v>
       </c>
       <c r="D30">
-        <v>19.78445763718863</v>
+        <v>19.78810240798472</v>
       </c>
       <c r="E30">
-        <v>6.20032</v>
+        <v>6.432260000000001</v>
       </c>
       <c r="F30">
-        <v>6.49432</v>
+        <v>6.726260000000001</v>
       </c>
       <c r="G30">
         <v>3.54</v>
@@ -3741,28 +3741,28 @@
         <v>1.685</v>
       </c>
       <c r="M30">
-        <v>0.359135896</v>
+        <v>0.371962178</v>
       </c>
       <c r="N30">
-        <v>1.325864104</v>
+        <v>1.313037822</v>
       </c>
       <c r="O30">
-        <v>0.1325864104</v>
+        <v>0.1313037822</v>
       </c>
       <c r="P30">
-        <v>1.1932776936</v>
+        <v>1.1817340398</v>
       </c>
       <c r="Q30">
-        <v>3.6832776936</v>
+        <v>3.6717340398</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1297354760707221</v>
+        <v>0.1308300962594378</v>
       </c>
       <c r="T30">
-        <v>1.298455120133861</v>
+        <v>1.315388546322357</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.691817272423249</v>
+        <v>4.530030469925896</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1073226683442009</v>
+        <v>0.1079751939174818</v>
       </c>
       <c r="C31">
-        <v>16.60184240798473</v>
+        <v>16.26462325541833</v>
       </c>
       <c r="D31">
-        <v>19.78810240798473</v>
+        <v>19.68282325541833</v>
       </c>
       <c r="E31">
-        <v>6.432259999999999</v>
+        <v>6.6642</v>
       </c>
       <c r="F31">
-        <v>6.726259999999999</v>
+        <v>6.9582</v>
       </c>
       <c r="G31">
         <v>3.54</v>
@@ -3823,45 +3823,45 @@
         <v>1.685</v>
       </c>
       <c r="M31">
-        <v>0.371962178</v>
+        <v>0.40218396</v>
       </c>
       <c r="N31">
-        <v>1.313037822</v>
+        <v>1.28281604</v>
       </c>
       <c r="O31">
-        <v>0.1313037822</v>
+        <v>0.128281604</v>
       </c>
       <c r="P31">
-        <v>1.1817340398</v>
+        <v>1.154534436</v>
       </c>
       <c r="Q31">
-        <v>3.6717340398</v>
+        <v>3.644534436</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1308300962594378</v>
+        <v>0.1319559913106883</v>
       </c>
       <c r="T31">
-        <v>1.315388546322356</v>
+        <v>1.332805784687666</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.1</v>
       </c>
       <c r="W31">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.530030469925896</v>
+        <v>4.189625066101591</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1079751939174818</v>
+        <v>0.1079752194907628</v>
       </c>
       <c r="C32">
-        <v>16.26462325541833</v>
+        <v>16.03267915135129</v>
       </c>
       <c r="D32">
-        <v>19.68282325541833</v>
+        <v>19.68281915135129</v>
       </c>
       <c r="E32">
-        <v>6.6642</v>
+        <v>6.89614</v>
       </c>
       <c r="F32">
-        <v>6.9582</v>
+        <v>7.19014</v>
       </c>
       <c r="G32">
         <v>3.54</v>
@@ -3905,28 +3905,28 @@
         <v>1.685</v>
       </c>
       <c r="M32">
-        <v>0.40218396</v>
+        <v>0.415590092</v>
       </c>
       <c r="N32">
-        <v>1.28281604</v>
+        <v>1.269409908</v>
       </c>
       <c r="O32">
-        <v>0.128281604</v>
+        <v>0.1269409908</v>
       </c>
       <c r="P32">
-        <v>1.154534436</v>
+        <v>1.1424689172</v>
       </c>
       <c r="Q32">
-        <v>3.644534436</v>
+        <v>3.6324689172</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1319559913106883</v>
+        <v>0.1331145210011055</v>
       </c>
       <c r="T32">
-        <v>1.332805784687666</v>
+        <v>1.350727870541826</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.189625066101591</v>
+        <v>4.054475870420895</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1079752194907628</v>
+        <v>0.1089832450640437</v>
       </c>
       <c r="C33">
-        <v>16.03267915135129</v>
+        <v>15.64028733631837</v>
       </c>
       <c r="D33">
-        <v>19.68281915135129</v>
+        <v>19.52236733631837</v>
       </c>
       <c r="E33">
-        <v>6.89614</v>
+        <v>7.128080000000001</v>
       </c>
       <c r="F33">
-        <v>7.19014</v>
+        <v>7.42208</v>
       </c>
       <c r="G33">
         <v>3.54</v>
@@ -3987,45 +3987,45 @@
         <v>1.685</v>
       </c>
       <c r="M33">
-        <v>0.415590092</v>
+        <v>0.454973504</v>
       </c>
       <c r="N33">
-        <v>1.269409908</v>
+        <v>1.230026496</v>
       </c>
       <c r="O33">
-        <v>0.1269409908</v>
+        <v>0.1230026496</v>
       </c>
       <c r="P33">
-        <v>1.1424689172</v>
+        <v>1.1070238464</v>
       </c>
       <c r="Q33">
-        <v>3.6324689172</v>
+        <v>3.5970238464</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1331145210011055</v>
+        <v>0.1343071250941819</v>
       </c>
       <c r="T33">
-        <v>1.350727870541826</v>
+        <v>1.369177076568167</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.1</v>
       </c>
       <c r="W33">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.054475870420895</v>
+        <v>3.70351236981044</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1089832450640437</v>
+        <v>0.1090147706373246</v>
       </c>
       <c r="C34">
-        <v>15.64028733631837</v>
+        <v>15.40337144888142</v>
       </c>
       <c r="D34">
-        <v>19.52236733631837</v>
+        <v>19.51739144888142</v>
       </c>
       <c r="E34">
-        <v>7.128080000000001</v>
+        <v>7.36002</v>
       </c>
       <c r="F34">
-        <v>7.42208</v>
+        <v>7.65402</v>
       </c>
       <c r="G34">
         <v>3.54</v>
@@ -4069,28 +4069,28 @@
         <v>1.685</v>
       </c>
       <c r="M34">
-        <v>0.454973504</v>
+        <v>0.469191426</v>
       </c>
       <c r="N34">
-        <v>1.230026496</v>
+        <v>1.215808574</v>
       </c>
       <c r="O34">
-        <v>0.1230026496</v>
+        <v>0.1215808574</v>
       </c>
       <c r="P34">
-        <v>1.1070238464</v>
+        <v>1.0942277166</v>
       </c>
       <c r="Q34">
-        <v>3.5970238464</v>
+        <v>3.5842277166</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1343071250941819</v>
+        <v>0.1355353293094398</v>
       </c>
       <c r="T34">
-        <v>1.369177076568167</v>
+        <v>1.388177005162458</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.70351236981044</v>
+        <v>3.591284722240426</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1090147706373246</v>
+        <v>0.1099030962106056</v>
       </c>
       <c r="C35">
-        <v>15.40337144888142</v>
+        <v>15.03225650881562</v>
       </c>
       <c r="D35">
-        <v>19.51739144888142</v>
+        <v>19.37821650881563</v>
       </c>
       <c r="E35">
-        <v>7.36002</v>
+        <v>7.59196</v>
       </c>
       <c r="F35">
-        <v>7.65402</v>
+        <v>7.88596</v>
       </c>
       <c r="G35">
         <v>3.54</v>
@@ -4151,45 +4151,45 @@
         <v>1.685</v>
       </c>
       <c r="M35">
-        <v>0.469191426</v>
+        <v>0.505490036</v>
       </c>
       <c r="N35">
-        <v>1.215808574</v>
+        <v>1.179509964</v>
       </c>
       <c r="O35">
-        <v>0.1215808574</v>
+        <v>0.1179509964</v>
       </c>
       <c r="P35">
-        <v>1.0942277166</v>
+        <v>1.0615589676</v>
       </c>
       <c r="Q35">
-        <v>3.5842277166</v>
+        <v>3.5515589676</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1355353293094398</v>
+        <v>0.1368007518342509</v>
       </c>
       <c r="T35">
-        <v>1.388177005162458</v>
+        <v>1.407752689168698</v>
       </c>
       <c r="U35">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V35">
         <v>0.1</v>
       </c>
       <c r="W35">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.591284722240426</v>
+        <v>3.333399038551968</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1099030962106056</v>
+        <v>0.1099598217838865</v>
       </c>
       <c r="C36">
-        <v>15.03225650881562</v>
+        <v>14.79149664068708</v>
       </c>
       <c r="D36">
-        <v>19.37821650881563</v>
+        <v>19.36939664068709</v>
       </c>
       <c r="E36">
-        <v>7.59196</v>
+        <v>7.823900000000001</v>
       </c>
       <c r="F36">
-        <v>7.88596</v>
+        <v>8.117900000000001</v>
       </c>
       <c r="G36">
         <v>3.54</v>
@@ -4233,28 +4233,28 @@
         <v>1.685</v>
       </c>
       <c r="M36">
-        <v>0.505490036</v>
+        <v>0.52035739</v>
       </c>
       <c r="N36">
-        <v>1.179509964</v>
+        <v>1.16464261</v>
       </c>
       <c r="O36">
-        <v>0.1179509964</v>
+        <v>0.116464261</v>
       </c>
       <c r="P36">
-        <v>1.0615589676</v>
+        <v>1.048178349</v>
       </c>
       <c r="Q36">
-        <v>3.5515589676</v>
+        <v>3.538178349</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1368007518342509</v>
+        <v>0.1381051104367485</v>
       </c>
       <c r="T36">
-        <v>1.407752689168698</v>
+        <v>1.427930701913591</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.333399038551968</v>
+        <v>3.238159066021912</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1099598217838865</v>
+        <v>0.1100165473571675</v>
       </c>
       <c r="C37">
-        <v>14.79149664068708</v>
+        <v>14.55074479751628</v>
       </c>
       <c r="D37">
-        <v>19.36939664068709</v>
+        <v>19.36058479751629</v>
       </c>
       <c r="E37">
-        <v>7.823900000000001</v>
+        <v>8.05584</v>
       </c>
       <c r="F37">
-        <v>8.117900000000001</v>
+        <v>8.34984</v>
       </c>
       <c r="G37">
         <v>3.54</v>
@@ -4315,28 +4315,28 @@
         <v>1.685</v>
       </c>
       <c r="M37">
-        <v>0.52035739</v>
+        <v>0.5352247440000001</v>
       </c>
       <c r="N37">
-        <v>1.16464261</v>
+        <v>1.149775255999999</v>
       </c>
       <c r="O37">
-        <v>0.116464261</v>
+        <v>0.1149775255999999</v>
       </c>
       <c r="P37">
-        <v>1.048178349</v>
+        <v>1.0347977304</v>
       </c>
       <c r="Q37">
-        <v>3.538178349</v>
+        <v>3.5247977304</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1381051104367485</v>
+        <v>0.1394502302455742</v>
       </c>
       <c r="T37">
-        <v>1.427930701913591</v>
+        <v>1.448739277556761</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.238159066021912</v>
+        <v>3.148210203076858</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1100165473571675</v>
+        <v>0.1100732729304484</v>
       </c>
       <c r="C38">
-        <v>14.55074479751629</v>
+        <v>14.31000096835566</v>
       </c>
       <c r="D38">
-        <v>19.36058479751629</v>
+        <v>19.35178096835567</v>
       </c>
       <c r="E38">
-        <v>8.055839999999998</v>
+        <v>8.28778</v>
       </c>
       <c r="F38">
-        <v>8.349839999999999</v>
+        <v>8.58178</v>
       </c>
       <c r="G38">
         <v>3.54</v>
@@ -4397,28 +4397,28 @@
         <v>1.685</v>
       </c>
       <c r="M38">
-        <v>0.535224744</v>
+        <v>0.550092098</v>
       </c>
       <c r="N38">
-        <v>1.149775256</v>
+        <v>1.134907902</v>
       </c>
       <c r="O38">
-        <v>0.1149775256</v>
+        <v>0.1134907902</v>
       </c>
       <c r="P38">
-        <v>1.0347977304</v>
+        <v>1.0214171118</v>
       </c>
       <c r="Q38">
-        <v>3.5247977304</v>
+        <v>3.5114171118</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1394502302455742</v>
+        <v>0.1408380522705531</v>
       </c>
       <c r="T38">
-        <v>1.448739277556761</v>
+        <v>1.47020844290289</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.148210203076859</v>
+        <v>3.063123440831538</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1100732729304484</v>
+        <v>0.1127975985037294</v>
       </c>
       <c r="C39">
-        <v>14.31000096835566</v>
+        <v>13.66446937413207</v>
       </c>
       <c r="D39">
-        <v>19.35178096835567</v>
+        <v>18.93818937413207</v>
       </c>
       <c r="E39">
-        <v>8.28778</v>
+        <v>8.51972</v>
       </c>
       <c r="F39">
-        <v>8.58178</v>
+        <v>8.81372</v>
       </c>
       <c r="G39">
         <v>3.54</v>
@@ -4479,45 +4479,45 @@
         <v>1.685</v>
       </c>
       <c r="M39">
-        <v>0.550092098</v>
+        <v>0.6337064680000001</v>
       </c>
       <c r="N39">
-        <v>1.134907902</v>
+        <v>1.051293531999999</v>
       </c>
       <c r="O39">
-        <v>0.1134907902</v>
+        <v>0.1051293531999999</v>
       </c>
       <c r="P39">
-        <v>1.0214171118</v>
+        <v>0.9461641787999995</v>
       </c>
       <c r="Q39">
-        <v>3.5114171118</v>
+        <v>3.436164178799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1408380522705531</v>
+        <v>0.1422706427479506</v>
       </c>
       <c r="T39">
-        <v>1.47020844290289</v>
+        <v>1.492370161969861</v>
       </c>
       <c r="U39">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V39">
         <v>0.1</v>
       </c>
       <c r="W39">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.063123440831538</v>
+        <v>2.658959763055471</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1127975985037294</v>
+        <v>0.1129245240770103</v>
       </c>
       <c r="C40">
-        <v>13.66446937413207</v>
+        <v>13.41369083936064</v>
       </c>
       <c r="D40">
-        <v>18.93818937413207</v>
+        <v>18.91935083936064</v>
       </c>
       <c r="E40">
-        <v>8.51972</v>
+        <v>8.751659999999999</v>
       </c>
       <c r="F40">
-        <v>8.81372</v>
+        <v>9.04566</v>
       </c>
       <c r="G40">
         <v>3.54</v>
@@ -4561,28 +4561,28 @@
         <v>1.685</v>
       </c>
       <c r="M40">
-        <v>0.6337064680000001</v>
+        <v>0.650382954</v>
       </c>
       <c r="N40">
-        <v>1.051293531999999</v>
+        <v>1.034617046</v>
       </c>
       <c r="O40">
-        <v>0.1051293531999999</v>
+        <v>0.1034617046</v>
       </c>
       <c r="P40">
-        <v>0.9461641787999995</v>
+        <v>0.9311553413999998</v>
       </c>
       <c r="Q40">
-        <v>3.436164178799999</v>
+        <v>3.4211553414</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1422706427479506</v>
+        <v>0.143750203404935</v>
       </c>
       <c r="T40">
-        <v>1.492370161969861</v>
+        <v>1.515258494776734</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.658959763055471</v>
+        <v>2.59078130759251</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1129245240770103</v>
+        <v>0.1130514496502913</v>
       </c>
       <c r="C41">
-        <v>13.41369083936064</v>
+        <v>13.1629497461538</v>
       </c>
       <c r="D41">
-        <v>18.91935083936064</v>
+        <v>18.9005497461538</v>
       </c>
       <c r="E41">
-        <v>8.751659999999999</v>
+        <v>8.983599999999999</v>
       </c>
       <c r="F41">
-        <v>9.04566</v>
+        <v>9.2776</v>
       </c>
       <c r="G41">
         <v>3.54</v>
@@ -4643,28 +4643,28 @@
         <v>1.685</v>
       </c>
       <c r="M41">
-        <v>0.650382954</v>
+        <v>0.6670594400000001</v>
       </c>
       <c r="N41">
-        <v>1.034617046</v>
+        <v>1.01794056</v>
       </c>
       <c r="O41">
-        <v>0.1034617046</v>
+        <v>0.101794056</v>
       </c>
       <c r="P41">
-        <v>0.9311553413999998</v>
+        <v>0.9161465039999996</v>
       </c>
       <c r="Q41">
-        <v>3.4211553414</v>
+        <v>3.406146504</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.143750203404935</v>
+        <v>0.1452790827504855</v>
       </c>
       <c r="T41">
-        <v>1.515258494776734</v>
+        <v>1.538909772010502</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.59078130759251</v>
+        <v>2.526011774902698</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1130514496502913</v>
+        <v>0.1146174752235722</v>
       </c>
       <c r="C42">
-        <v>13.1629497461538</v>
+        <v>12.70207668738251</v>
       </c>
       <c r="D42">
-        <v>18.9005497461538</v>
+        <v>18.67161668738251</v>
       </c>
       <c r="E42">
-        <v>8.983599999999999</v>
+        <v>9.215540000000001</v>
       </c>
       <c r="F42">
-        <v>9.2776</v>
+        <v>9.509540000000001</v>
       </c>
       <c r="G42">
         <v>3.54</v>
@@ -4725,45 +4725,45 @@
         <v>1.685</v>
       </c>
       <c r="M42">
-        <v>0.6670594400000001</v>
+        <v>0.7208231320000001</v>
       </c>
       <c r="N42">
-        <v>1.01794056</v>
+        <v>0.9641768679999995</v>
       </c>
       <c r="O42">
-        <v>0.101794056</v>
+        <v>0.09641768679999996</v>
       </c>
       <c r="P42">
-        <v>0.9161465039999996</v>
+        <v>0.8677591811999995</v>
       </c>
       <c r="Q42">
-        <v>3.406146504</v>
+        <v>3.3577591812</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1452790827504855</v>
+        <v>0.1468597885145292</v>
       </c>
       <c r="T42">
-        <v>1.538909772010502</v>
+        <v>1.563362787455584</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.1</v>
       </c>
       <c r="W42">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.526011774902698</v>
+        <v>2.337605336450273</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1146174752235722</v>
+        <v>0.1147795007968532</v>
       </c>
       <c r="C43">
-        <v>12.70207668738251</v>
+        <v>12.44676679031922</v>
       </c>
       <c r="D43">
-        <v>18.67161668738251</v>
+        <v>18.64824679031922</v>
       </c>
       <c r="E43">
-        <v>9.215540000000001</v>
+        <v>9.447480000000001</v>
       </c>
       <c r="F43">
-        <v>9.509540000000001</v>
+        <v>9.741480000000001</v>
       </c>
       <c r="G43">
         <v>3.54</v>
@@ -4807,28 +4807,28 @@
         <v>1.685</v>
       </c>
       <c r="M43">
-        <v>0.7208231320000001</v>
+        <v>0.7384041840000002</v>
       </c>
       <c r="N43">
-        <v>0.9641768679999995</v>
+        <v>0.9465958159999994</v>
       </c>
       <c r="O43">
-        <v>0.09641768679999996</v>
+        <v>0.09465958159999995</v>
       </c>
       <c r="P43">
-        <v>0.8677591811999995</v>
+        <v>0.8519362343999994</v>
       </c>
       <c r="Q43">
-        <v>3.3577591812</v>
+        <v>3.341936234399999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1468597885145292</v>
+        <v>0.1484950013738848</v>
       </c>
       <c r="T43">
-        <v>1.563362787455584</v>
+        <v>1.588659010329807</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.337605336450273</v>
+        <v>2.28194806653479</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1147795007968532</v>
+        <v>0.1149415263701341</v>
       </c>
       <c r="C44">
-        <v>12.44676679031922</v>
+        <v>12.19151532090832</v>
       </c>
       <c r="D44">
-        <v>18.64824679031922</v>
+        <v>18.62493532090832</v>
       </c>
       <c r="E44">
-        <v>9.447479999999999</v>
+        <v>9.679419999999999</v>
       </c>
       <c r="F44">
-        <v>9.741479999999999</v>
+        <v>9.973419999999999</v>
       </c>
       <c r="G44">
         <v>3.54</v>
@@ -4889,28 +4889,28 @@
         <v>1.685</v>
       </c>
       <c r="M44">
-        <v>0.738404184</v>
+        <v>0.755985236</v>
       </c>
       <c r="N44">
-        <v>0.9465958159999996</v>
+        <v>0.9290147639999996</v>
       </c>
       <c r="O44">
-        <v>0.09465958159999997</v>
+        <v>0.09290147639999996</v>
       </c>
       <c r="P44">
-        <v>0.8519362343999997</v>
+        <v>0.8361132875999997</v>
       </c>
       <c r="Q44">
-        <v>3.3419362344</v>
+        <v>3.3261132876</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1484950013738848</v>
+        <v>0.1501875901230423</v>
       </c>
       <c r="T44">
-        <v>1.588659010329806</v>
+        <v>1.614842819971546</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.28194806653479</v>
+        <v>2.228879506847935</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1149415263701341</v>
+        <v>0.1151035519434151</v>
       </c>
       <c r="C45">
-        <v>12.19151532090832</v>
+        <v>11.93632206030876</v>
       </c>
       <c r="D45">
-        <v>18.62493532090832</v>
+        <v>18.60168206030876</v>
       </c>
       <c r="E45">
-        <v>9.679419999999999</v>
+        <v>9.911359999999998</v>
       </c>
       <c r="F45">
-        <v>9.973419999999999</v>
+        <v>10.20536</v>
       </c>
       <c r="G45">
         <v>3.54</v>
@@ -4971,28 +4971,28 @@
         <v>1.685</v>
       </c>
       <c r="M45">
-        <v>0.755985236</v>
+        <v>0.7735662879999999</v>
       </c>
       <c r="N45">
-        <v>0.9290147639999996</v>
+        <v>0.9114337119999997</v>
       </c>
       <c r="O45">
-        <v>0.09290147639999996</v>
+        <v>0.09114337119999998</v>
       </c>
       <c r="P45">
-        <v>0.8361132875999997</v>
+        <v>0.8202903407999997</v>
       </c>
       <c r="Q45">
-        <v>3.3261132876</v>
+        <v>3.3102903408</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1501875901230423</v>
+        <v>0.1519406284703841</v>
       </c>
       <c r="T45">
-        <v>1.614842819971546</v>
+        <v>1.641961765671919</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.228879506847935</v>
+        <v>2.178223154419573</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1151035519434151</v>
+        <v>0.115265577516696</v>
       </c>
       <c r="C46">
-        <v>11.93632206030876</v>
+        <v>11.68118679077102</v>
       </c>
       <c r="D46">
-        <v>18.60168206030876</v>
+        <v>18.57848679077102</v>
       </c>
       <c r="E46">
-        <v>9.911359999999998</v>
+        <v>10.1433</v>
       </c>
       <c r="F46">
-        <v>10.20536</v>
+        <v>10.4373</v>
       </c>
       <c r="G46">
         <v>3.54</v>
@@ -5053,28 +5053,28 @@
         <v>1.685</v>
       </c>
       <c r="M46">
-        <v>0.7735662879999999</v>
+        <v>0.7911473400000001</v>
       </c>
       <c r="N46">
-        <v>0.9114337119999997</v>
+        <v>0.8938526599999995</v>
       </c>
       <c r="O46">
-        <v>0.09114337119999998</v>
+        <v>0.08938526599999996</v>
       </c>
       <c r="P46">
-        <v>0.8202903407999997</v>
+        <v>0.8044673939999996</v>
       </c>
       <c r="Q46">
-        <v>3.3102903408</v>
+        <v>3.294467394</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1519406284703841</v>
+        <v>0.15375741366672</v>
       </c>
       <c r="T46">
-        <v>1.641961765671919</v>
+        <v>1.670066854852306</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.178223154419573</v>
+        <v>2.129818195432471</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.115265577516696</v>
+        <v>0.115427603089977</v>
       </c>
       <c r="C47">
-        <v>11.68118679077102</v>
+        <v>11.42610929563034</v>
       </c>
       <c r="D47">
-        <v>18.57848679077102</v>
+        <v>18.55534929563034</v>
       </c>
       <c r="E47">
-        <v>10.1433</v>
+        <v>10.37524</v>
       </c>
       <c r="F47">
-        <v>10.4373</v>
+        <v>10.66924</v>
       </c>
       <c r="G47">
         <v>3.54</v>
@@ -5135,28 +5135,28 @@
         <v>1.685</v>
       </c>
       <c r="M47">
-        <v>0.7911473400000001</v>
+        <v>0.8087283920000001</v>
       </c>
       <c r="N47">
-        <v>0.8938526599999995</v>
+        <v>0.8762716079999995</v>
       </c>
       <c r="O47">
-        <v>0.08938526599999996</v>
+        <v>0.08762716079999995</v>
       </c>
       <c r="P47">
-        <v>0.8044673939999996</v>
+        <v>0.7886444471999995</v>
       </c>
       <c r="Q47">
-        <v>3.294467394</v>
+        <v>3.2786444472</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.15375741366672</v>
+        <v>0.155641487203661</v>
       </c>
       <c r="T47">
-        <v>1.670066854852306</v>
+        <v>1.699212873261595</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.129818195432471</v>
+        <v>2.083517799879591</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.115427603089977</v>
+        <v>0.1155896286632579</v>
       </c>
       <c r="C48">
-        <v>11.42610929563034</v>
+        <v>11.17108935929992</v>
       </c>
       <c r="D48">
-        <v>18.55534929563034</v>
+        <v>18.53226935929992</v>
       </c>
       <c r="E48">
-        <v>10.37524</v>
+        <v>10.60718</v>
       </c>
       <c r="F48">
-        <v>10.66924</v>
+        <v>10.90118</v>
       </c>
       <c r="G48">
         <v>3.54</v>
@@ -5217,28 +5217,28 @@
         <v>1.685</v>
       </c>
       <c r="M48">
-        <v>0.8087283920000001</v>
+        <v>0.8263094440000001</v>
       </c>
       <c r="N48">
-        <v>0.8762716079999995</v>
+        <v>0.8586905559999995</v>
       </c>
       <c r="O48">
-        <v>0.08762716079999995</v>
+        <v>0.08586905559999997</v>
       </c>
       <c r="P48">
-        <v>0.7886444471999995</v>
+        <v>0.7728215003999996</v>
       </c>
       <c r="Q48">
-        <v>3.2786444472</v>
+        <v>3.2628215004</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.155641487203661</v>
+        <v>0.1575966578552036</v>
       </c>
       <c r="T48">
-        <v>1.699212873261595</v>
+        <v>1.729458741422179</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.083517799879591</v>
+        <v>2.039187633924706</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1155896286632579</v>
+        <v>0.1218860542365389</v>
       </c>
       <c r="C49">
-        <v>11.17108935929992</v>
+        <v>10.08466554498747</v>
       </c>
       <c r="D49">
-        <v>18.53226935929992</v>
+        <v>17.67778554498748</v>
       </c>
       <c r="E49">
-        <v>10.60718</v>
+        <v>10.83912</v>
       </c>
       <c r="F49">
-        <v>10.90118</v>
+        <v>11.13312</v>
       </c>
       <c r="G49">
         <v>3.54</v>
@@ -5299,45 +5299,45 @@
         <v>1.685</v>
       </c>
       <c r="M49">
-        <v>0.8263094440000001</v>
+        <v>1.0019808</v>
       </c>
       <c r="N49">
-        <v>0.8586905559999995</v>
+        <v>0.6830191999999997</v>
       </c>
       <c r="O49">
-        <v>0.08586905559999997</v>
+        <v>0.06830191999999997</v>
       </c>
       <c r="P49">
-        <v>0.7728215003999996</v>
+        <v>0.6147172799999997</v>
       </c>
       <c r="Q49">
-        <v>3.2628215004</v>
+        <v>3.10471728</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1575966578552036</v>
+        <v>0.1596270273779593</v>
       </c>
       <c r="T49">
-        <v>1.729458741422179</v>
+        <v>1.760867912204324</v>
       </c>
       <c r="U49">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V49">
         <v>0.1</v>
       </c>
       <c r="W49">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.039187633924706</v>
+        <v>1.681668950143556</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1218860542365389</v>
+        <v>0.1221758798098198</v>
       </c>
       <c r="C50">
-        <v>10.08466554498748</v>
+        <v>9.815286481443124</v>
       </c>
       <c r="D50">
-        <v>17.67778554498748</v>
+        <v>17.64034648144312</v>
       </c>
       <c r="E50">
-        <v>10.83912</v>
+        <v>11.07106</v>
       </c>
       <c r="F50">
-        <v>11.13312</v>
+        <v>11.36506</v>
       </c>
       <c r="G50">
         <v>3.54</v>
@@ -5381,28 +5381,28 @@
         <v>1.685</v>
       </c>
       <c r="M50">
-        <v>1.0019808</v>
+        <v>1.0228554</v>
       </c>
       <c r="N50">
-        <v>0.6830191999999997</v>
+        <v>0.6621445999999998</v>
       </c>
       <c r="O50">
-        <v>0.06830191999999997</v>
+        <v>0.06621445999999998</v>
       </c>
       <c r="P50">
-        <v>0.6147172799999997</v>
+        <v>0.5959301399999998</v>
       </c>
       <c r="Q50">
-        <v>3.10471728</v>
+        <v>3.08593014</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1596270273779593</v>
+        <v>0.1617370192349408</v>
       </c>
       <c r="T50">
-        <v>1.760867912204324</v>
+        <v>1.793508815174004</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.681668950143556</v>
+        <v>1.64734917565083</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1221758798098198</v>
+        <v>0.1224657053831008</v>
       </c>
       <c r="C51">
-        <v>9.815286481443124</v>
+        <v>9.546065664097737</v>
       </c>
       <c r="D51">
-        <v>17.64034648144312</v>
+        <v>17.60306566409774</v>
       </c>
       <c r="E51">
-        <v>11.07106</v>
+        <v>11.303</v>
       </c>
       <c r="F51">
-        <v>11.36506</v>
+        <v>11.597</v>
       </c>
       <c r="G51">
         <v>3.54</v>
@@ -5463,28 +5463,28 @@
         <v>1.685</v>
       </c>
       <c r="M51">
-        <v>1.0228554</v>
+        <v>1.04373</v>
       </c>
       <c r="N51">
-        <v>0.6621445999999998</v>
+        <v>0.6412699999999998</v>
       </c>
       <c r="O51">
-        <v>0.06621445999999998</v>
+        <v>0.06412699999999998</v>
       </c>
       <c r="P51">
-        <v>0.5959301399999998</v>
+        <v>0.5771429999999999</v>
       </c>
       <c r="Q51">
-        <v>3.08593014</v>
+        <v>3.067143</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1617370192349408</v>
+        <v>0.1639314107662015</v>
       </c>
       <c r="T51">
-        <v>1.793508815174004</v>
+        <v>1.827455354262471</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.64734917565083</v>
+        <v>1.614402192137813</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1224657053831008</v>
+        <v>0.1227555309563817</v>
       </c>
       <c r="C52">
-        <v>9.546065664097737</v>
+        <v>9.277002091762498</v>
       </c>
       <c r="D52">
-        <v>17.60306566409774</v>
+        <v>17.5659420917625</v>
       </c>
       <c r="E52">
-        <v>11.303</v>
+        <v>11.53494</v>
       </c>
       <c r="F52">
-        <v>11.597</v>
+        <v>11.82894</v>
       </c>
       <c r="G52">
         <v>3.54</v>
@@ -5545,28 +5545,28 @@
         <v>1.685</v>
       </c>
       <c r="M52">
-        <v>1.04373</v>
+        <v>1.0646046</v>
       </c>
       <c r="N52">
-        <v>0.6412699999999998</v>
+        <v>0.6203953999999996</v>
       </c>
       <c r="O52">
-        <v>0.06412699999999998</v>
+        <v>0.06203953999999996</v>
       </c>
       <c r="P52">
-        <v>0.5771429999999999</v>
+        <v>0.5583558599999996</v>
       </c>
       <c r="Q52">
-        <v>3.067143</v>
+        <v>3.04835586</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1639314107662015</v>
+        <v>0.1662153692987381</v>
       </c>
       <c r="T52">
-        <v>1.827455354262471</v>
+        <v>1.862787466374956</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.614402192137813</v>
+        <v>1.582747247193934</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1227555309563817</v>
+        <v>0.1230453565296626</v>
       </c>
       <c r="C53">
-        <v>9.277002091762498</v>
+        <v>9.008094771676527</v>
       </c>
       <c r="D53">
-        <v>17.5659420917625</v>
+        <v>17.52897477167653</v>
       </c>
       <c r="E53">
-        <v>11.53494</v>
+        <v>11.76688</v>
       </c>
       <c r="F53">
-        <v>11.82894</v>
+        <v>12.06088</v>
       </c>
       <c r="G53">
         <v>3.54</v>
@@ -5627,28 +5627,28 @@
         <v>1.685</v>
       </c>
       <c r="M53">
-        <v>1.0646046</v>
+        <v>1.0854792</v>
       </c>
       <c r="N53">
-        <v>0.6203953999999996</v>
+        <v>0.5995207999999996</v>
       </c>
       <c r="O53">
-        <v>0.06203953999999996</v>
+        <v>0.05995207999999996</v>
       </c>
       <c r="P53">
-        <v>0.5583558599999996</v>
+        <v>0.5395687199999997</v>
       </c>
       <c r="Q53">
-        <v>3.04835586</v>
+        <v>3.02956872</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1662153692987381</v>
+        <v>0.1685944927701305</v>
       </c>
       <c r="T53">
-        <v>1.862787466374956</v>
+        <v>1.899591749825463</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.582747247193934</v>
+        <v>1.552309800132513</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1230453565296626</v>
+        <v>0.1233351821029436</v>
       </c>
       <c r="C54">
-        <v>9.008094771676527</v>
+        <v>8.739342719418433</v>
       </c>
       <c r="D54">
-        <v>17.52897477167653</v>
+        <v>17.49216271941843</v>
       </c>
       <c r="E54">
-        <v>11.76688</v>
+        <v>11.99882</v>
       </c>
       <c r="F54">
-        <v>12.06088</v>
+        <v>12.29282</v>
       </c>
       <c r="G54">
         <v>3.54</v>
@@ -5709,28 +5709,28 @@
         <v>1.685</v>
       </c>
       <c r="M54">
-        <v>1.0854792</v>
+        <v>1.1063538</v>
       </c>
       <c r="N54">
-        <v>0.5995207999999996</v>
+        <v>0.5786461999999997</v>
       </c>
       <c r="O54">
-        <v>0.05995207999999996</v>
+        <v>0.05786461999999997</v>
       </c>
       <c r="P54">
-        <v>0.5395687199999997</v>
+        <v>0.5207815799999997</v>
       </c>
       <c r="Q54">
-        <v>3.02956872</v>
+        <v>3.01078158</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1685944927701305</v>
+        <v>0.1710748555381778</v>
       </c>
       <c r="T54">
-        <v>1.899591749825463</v>
+        <v>1.937962172997267</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.552309800132513</v>
+        <v>1.523020935979069</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1233351821029436</v>
+        <v>0.1521727409105935</v>
       </c>
       <c r="C55">
-        <v>8.739342719418433</v>
+        <v>5.484054030501611</v>
       </c>
       <c r="D55">
-        <v>17.49216271941843</v>
+        <v>14.46881403050161</v>
       </c>
       <c r="E55">
-        <v>11.99882</v>
+        <v>12.23076</v>
       </c>
       <c r="F55">
-        <v>12.29282</v>
+        <v>12.52476</v>
       </c>
       <c r="G55">
         <v>3.54</v>
@@ -5791,45 +5791,45 @@
         <v>1.685</v>
       </c>
       <c r="M55">
-        <v>1.1063538</v>
+        <v>1.838634768</v>
       </c>
       <c r="N55">
-        <v>0.5786461999999997</v>
+        <v>-0.1536347680000008</v>
       </c>
       <c r="O55">
-        <v>0.05786461999999997</v>
+        <v>-0.01536347680000008</v>
       </c>
       <c r="P55">
-        <v>0.5207815799999997</v>
+        <v>-0.1382712912000007</v>
       </c>
       <c r="Q55">
-        <v>3.01078158</v>
+        <v>2.3517287088</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1710748555381778</v>
+        <v>0.1742729364678557</v>
       </c>
       <c r="T55">
-        <v>1.937962172997267</v>
+        <v>1.987435467867768</v>
       </c>
       <c r="U55">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1</v>
+        <v>0.09164408447648802</v>
       </c>
       <c r="W55">
-        <v>0.081</v>
+        <v>0.1333466483988516</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.523020935979069</v>
+        <v>0.9164408447648801</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1521727409105935</v>
+        <v>0.1531827409105935</v>
       </c>
       <c r="C56">
-        <v>5.484054030501611</v>
+        <v>5.165053870294061</v>
       </c>
       <c r="D56">
-        <v>14.46881403050161</v>
+        <v>14.38175387029406</v>
       </c>
       <c r="E56">
-        <v>12.23076</v>
+        <v>12.4627</v>
       </c>
       <c r="F56">
-        <v>12.52476</v>
+        <v>12.7567</v>
       </c>
       <c r="G56">
         <v>3.54</v>
@@ -5873,37 +5873,37 @@
         <v>1.685</v>
       </c>
       <c r="M56">
-        <v>1.838634768</v>
+        <v>1.87268356</v>
       </c>
       <c r="N56">
-        <v>-0.1536347680000008</v>
+        <v>-0.1876835600000006</v>
       </c>
       <c r="O56">
-        <v>-0.01536347680000008</v>
+        <v>-0.01876835600000007</v>
       </c>
       <c r="P56">
-        <v>-0.1382712912000007</v>
+        <v>-0.1689152040000006</v>
       </c>
       <c r="Q56">
-        <v>2.3517287088</v>
+        <v>2.321084796</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1742729364678557</v>
+        <v>0.1771278906115859</v>
       </c>
       <c r="T56">
-        <v>1.987435467867768</v>
+        <v>2.031600700487052</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.09164408447648802</v>
+        <v>0.08997782839509733</v>
       </c>
       <c r="W56">
-        <v>0.1333466483988516</v>
+        <v>0.1335912547915997</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9164408447648801</v>
+        <v>0.8997782839509733</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1531827409105935</v>
+        <v>0.1541927409105935</v>
       </c>
       <c r="C57">
-        <v>5.165053870294061</v>
+        <v>4.847095141387179</v>
       </c>
       <c r="D57">
-        <v>14.38175387029406</v>
+        <v>14.29573514138718</v>
       </c>
       <c r="E57">
-        <v>12.4627</v>
+        <v>12.69464</v>
       </c>
       <c r="F57">
-        <v>12.7567</v>
+        <v>12.98864</v>
       </c>
       <c r="G57">
         <v>3.54</v>
@@ -5955,37 +5955,37 @@
         <v>1.685</v>
       </c>
       <c r="M57">
-        <v>1.87268356</v>
+        <v>1.906732352</v>
       </c>
       <c r="N57">
-        <v>-0.1876835600000006</v>
+        <v>-0.2217323520000005</v>
       </c>
       <c r="O57">
-        <v>-0.01876835600000007</v>
+        <v>-0.02217323520000005</v>
       </c>
       <c r="P57">
-        <v>-0.1689152040000006</v>
+        <v>-0.1995591168000005</v>
       </c>
       <c r="Q57">
-        <v>2.321084796</v>
+        <v>2.2904408832</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1771278906115859</v>
+        <v>0.1801126153982127</v>
       </c>
       <c r="T57">
-        <v>2.031600700487052</v>
+        <v>2.077773443679939</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.08997782839509733</v>
+        <v>0.08837108145947059</v>
       </c>
       <c r="W57">
-        <v>0.1335912547915997</v>
+        <v>0.1338271252417497</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8997782839509733</v>
+        <v>0.8837108145947059</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1541927409105935</v>
+        <v>0.1552027409105935</v>
       </c>
       <c r="C58">
-        <v>4.847095141387179</v>
+        <v>4.530159268164816</v>
       </c>
       <c r="D58">
-        <v>14.29573514138718</v>
+        <v>14.21073926816482</v>
       </c>
       <c r="E58">
-        <v>12.69464</v>
+        <v>12.92658</v>
       </c>
       <c r="F58">
-        <v>12.98864</v>
+        <v>13.22058</v>
       </c>
       <c r="G58">
         <v>3.54</v>
@@ -6037,37 +6037,37 @@
         <v>1.685</v>
       </c>
       <c r="M58">
-        <v>1.906732352</v>
+        <v>1.940781144</v>
       </c>
       <c r="N58">
-        <v>-0.2217323520000005</v>
+        <v>-0.2557811440000008</v>
       </c>
       <c r="O58">
-        <v>-0.02217323520000005</v>
+        <v>-0.02557811440000009</v>
       </c>
       <c r="P58">
-        <v>-0.1995591168000005</v>
+        <v>-0.2302030296000008</v>
       </c>
       <c r="Q58">
-        <v>2.2904408832</v>
+        <v>2.2597969704</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1801126153982127</v>
+        <v>0.18323616459352</v>
       </c>
       <c r="T58">
-        <v>2.077773443679939</v>
+        <v>2.126093756323658</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.08837108145947059</v>
+        <v>0.08682071160930444</v>
       </c>
       <c r="W58">
-        <v>0.1338271252417497</v>
+        <v>0.1340547195357541</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8837108145947059</v>
+        <v>0.8682071160930442</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1552027409105935</v>
+        <v>0.1562127409105935</v>
       </c>
       <c r="C59">
-        <v>4.530159268164816</v>
+        <v>4.214228114168135</v>
       </c>
       <c r="D59">
-        <v>14.21073926816482</v>
+        <v>14.12674811416814</v>
       </c>
       <c r="E59">
-        <v>12.92658</v>
+        <v>13.15852</v>
       </c>
       <c r="F59">
-        <v>13.22058</v>
+        <v>13.45252</v>
       </c>
       <c r="G59">
         <v>3.54</v>
@@ -6119,37 +6119,37 @@
         <v>1.685</v>
       </c>
       <c r="M59">
-        <v>1.940781144</v>
+        <v>1.974829936</v>
       </c>
       <c r="N59">
-        <v>-0.2557811440000008</v>
+        <v>-0.2898299360000007</v>
       </c>
       <c r="O59">
-        <v>-0.02557811440000009</v>
+        <v>-0.02898299360000008</v>
       </c>
       <c r="P59">
-        <v>-0.2302030296000008</v>
+        <v>-0.2608469424000007</v>
       </c>
       <c r="Q59">
-        <v>2.2597969704</v>
+        <v>2.2291530576</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.18323616459352</v>
+        <v>0.1865084542266991</v>
       </c>
       <c r="T59">
-        <v>2.126093756323658</v>
+        <v>2.176715036236127</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.08682071160930444</v>
+        <v>0.08532380278845436</v>
       </c>
       <c r="W59">
-        <v>0.1340547195357541</v>
+        <v>0.1342744657506549</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8682071160930442</v>
+        <v>0.8532380278845435</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1562127409105935</v>
+        <v>0.1572227409105935</v>
       </c>
       <c r="C60">
-        <v>4.214228114168142</v>
+        <v>3.899283969193856</v>
       </c>
       <c r="D60">
-        <v>14.12674811416814</v>
+        <v>14.04374396919385</v>
       </c>
       <c r="E60">
-        <v>13.15852</v>
+        <v>13.39046</v>
       </c>
       <c r="F60">
-        <v>13.45252</v>
+        <v>13.68446</v>
       </c>
       <c r="G60">
         <v>3.54</v>
@@ -6201,37 +6201,37 @@
         <v>1.685</v>
       </c>
       <c r="M60">
-        <v>1.974829936</v>
+        <v>2.008878728</v>
       </c>
       <c r="N60">
-        <v>-0.2898299360000003</v>
+        <v>-0.3238787280000004</v>
       </c>
       <c r="O60">
-        <v>-0.02898299360000003</v>
+        <v>-0.03238787280000004</v>
       </c>
       <c r="P60">
-        <v>-0.2608469424000003</v>
+        <v>-0.2914908552000003</v>
       </c>
       <c r="Q60">
-        <v>2.2291530576</v>
+        <v>2.1985091448</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1865084542266991</v>
+        <v>0.1899403677444234</v>
       </c>
       <c r="T60">
-        <v>2.176715036236126</v>
+        <v>2.229805646876031</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.08532380278845438</v>
+        <v>0.08387763663949752</v>
       </c>
       <c r="W60">
-        <v>0.1342744657506549</v>
+        <v>0.1344867629413218</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8532380278845437</v>
+        <v>0.8387763663949751</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1572227409105935</v>
+        <v>0.1582327409105935</v>
       </c>
       <c r="C61">
-        <v>3.899283969193856</v>
+        <v>3.585309536844704</v>
       </c>
       <c r="D61">
-        <v>14.04374396919385</v>
+        <v>13.9617095368447</v>
       </c>
       <c r="E61">
-        <v>13.39046</v>
+        <v>13.6224</v>
       </c>
       <c r="F61">
-        <v>13.68446</v>
+        <v>13.9164</v>
       </c>
       <c r="G61">
         <v>3.54</v>
@@ -6283,37 +6283,37 @@
         <v>1.685</v>
       </c>
       <c r="M61">
-        <v>2.008878728</v>
+        <v>2.04292752</v>
       </c>
       <c r="N61">
-        <v>-0.3238787280000004</v>
+        <v>-0.3579275200000005</v>
       </c>
       <c r="O61">
-        <v>-0.03238787280000004</v>
+        <v>-0.03579275200000005</v>
       </c>
       <c r="P61">
-        <v>-0.2914908552000003</v>
+        <v>-0.3221347680000005</v>
       </c>
       <c r="Q61">
-        <v>2.1985091448</v>
+        <v>2.167865232</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1899403677444234</v>
+        <v>0.193543876938034</v>
       </c>
       <c r="T61">
-        <v>2.229805646876031</v>
+        <v>2.285550788047932</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.08387763663949752</v>
+        <v>0.08247967602883922</v>
       </c>
       <c r="W61">
-        <v>0.1344867629413218</v>
+        <v>0.1346919835589664</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8387763663949751</v>
+        <v>0.8247967602883922</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1582327409105935</v>
+        <v>0.1592427409105935</v>
       </c>
       <c r="C62">
-        <v>3.585309536844704</v>
+        <v>3.272287922513735</v>
       </c>
       <c r="D62">
-        <v>13.9617095368447</v>
+        <v>13.88062792251373</v>
       </c>
       <c r="E62">
-        <v>13.6224</v>
+        <v>13.85434</v>
       </c>
       <c r="F62">
-        <v>13.9164</v>
+        <v>14.14834</v>
       </c>
       <c r="G62">
         <v>3.54</v>
@@ -6365,37 +6365,37 @@
         <v>1.685</v>
       </c>
       <c r="M62">
-        <v>2.04292752</v>
+        <v>2.076976312</v>
       </c>
       <c r="N62">
-        <v>-0.3579275200000005</v>
+        <v>-0.3919763120000006</v>
       </c>
       <c r="O62">
-        <v>-0.03579275200000005</v>
+        <v>-0.03919763120000006</v>
       </c>
       <c r="P62">
-        <v>-0.3221347680000005</v>
+        <v>-0.3527786808000005</v>
       </c>
       <c r="Q62">
-        <v>2.167865232</v>
+        <v>2.1372213192</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.193543876938034</v>
+        <v>0.1973321814749067</v>
       </c>
       <c r="T62">
-        <v>2.285550788047932</v>
+        <v>2.344154654408136</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.08247967602883922</v>
+        <v>0.08112755019230088</v>
       </c>
       <c r="W62">
-        <v>0.1346919835589664</v>
+        <v>0.1348904756317702</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8247967602883922</v>
+        <v>0.8112755019230087</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1592427409105935</v>
+        <v>0.1945601876285584</v>
       </c>
       <c r="C63">
-        <v>3.272287922513735</v>
+        <v>0.6973660667665484</v>
       </c>
       <c r="D63">
-        <v>13.88062792251373</v>
+        <v>11.53764606676655</v>
       </c>
       <c r="E63">
-        <v>13.85434</v>
+        <v>14.08628</v>
       </c>
       <c r="F63">
-        <v>14.14834</v>
+        <v>14.38028</v>
       </c>
       <c r="G63">
         <v>3.54</v>
@@ -6447,45 +6447,45 @@
         <v>1.685</v>
       </c>
       <c r="M63">
-        <v>2.076976312</v>
+        <v>2.887560224</v>
       </c>
       <c r="N63">
-        <v>-0.3919763120000006</v>
+        <v>-1.202560224</v>
       </c>
       <c r="O63">
-        <v>-0.03919763120000006</v>
+        <v>-0.1202560224000001</v>
       </c>
       <c r="P63">
-        <v>-0.3527786808000005</v>
+        <v>-1.0823042016</v>
       </c>
       <c r="Q63">
-        <v>2.1372213192</v>
+        <v>1.4076957984</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1973321814749067</v>
+        <v>0.203497361824154</v>
       </c>
       <c r="T63">
-        <v>2.344154654408136</v>
+        <v>2.439528033648682</v>
       </c>
       <c r="U63">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.08112755019230088</v>
+        <v>0.05835376128245212</v>
       </c>
       <c r="W63">
-        <v>0.1348904756317702</v>
+        <v>0.1890825647344836</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.8112755019230087</v>
+        <v>0.5835376128245211</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1945601876285584</v>
+        <v>0.1961101876285584</v>
       </c>
       <c r="C64">
-        <v>0.6973660667665484</v>
+        <v>0.3805834568329249</v>
       </c>
       <c r="D64">
-        <v>11.53764606676655</v>
+        <v>11.45280345683292</v>
       </c>
       <c r="E64">
-        <v>14.08628</v>
+        <v>14.31822</v>
       </c>
       <c r="F64">
-        <v>14.38028</v>
+        <v>14.61222</v>
       </c>
       <c r="G64">
         <v>3.54</v>
@@ -6529,37 +6529,37 @@
         <v>1.685</v>
       </c>
       <c r="M64">
-        <v>2.887560224</v>
+        <v>2.934133776</v>
       </c>
       <c r="N64">
-        <v>-1.202560224</v>
+        <v>-1.249133776</v>
       </c>
       <c r="O64">
-        <v>-0.1202560224000001</v>
+        <v>-0.1249133776</v>
       </c>
       <c r="P64">
-        <v>-1.0823042016</v>
+        <v>-1.1242203984</v>
       </c>
       <c r="Q64">
-        <v>1.4076957984</v>
+        <v>1.3657796016</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.203497361824154</v>
+        <v>0.2077594526842662</v>
       </c>
       <c r="T64">
-        <v>2.439528033648682</v>
+        <v>2.505461223747295</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05835376128245212</v>
+        <v>0.05742751110336558</v>
       </c>
       <c r="W64">
-        <v>0.1890825647344836</v>
+        <v>0.1892685557704442</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5835376128245211</v>
+        <v>0.5742751110336557</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1961101876285584</v>
+        <v>0.1976601876285584</v>
       </c>
       <c r="C65">
-        <v>0.3805834568329249</v>
+        <v>0.06503952626661835</v>
       </c>
       <c r="D65">
-        <v>11.45280345683292</v>
+        <v>11.36919952626662</v>
       </c>
       <c r="E65">
-        <v>14.31822</v>
+        <v>14.55016</v>
       </c>
       <c r="F65">
-        <v>14.61222</v>
+        <v>14.84416</v>
       </c>
       <c r="G65">
         <v>3.54</v>
@@ -6611,37 +6611,37 @@
         <v>1.685</v>
       </c>
       <c r="M65">
-        <v>2.934133776</v>
+        <v>2.980707328</v>
       </c>
       <c r="N65">
-        <v>-1.249133776</v>
+        <v>-1.295707328000001</v>
       </c>
       <c r="O65">
-        <v>-0.1249133776</v>
+        <v>-0.1295707328000001</v>
       </c>
       <c r="P65">
-        <v>-1.1242203984</v>
+        <v>-1.166136595200001</v>
       </c>
       <c r="Q65">
-        <v>1.3657796016</v>
+        <v>1.3238634048</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2077594526842662</v>
+        <v>0.2122583263699403</v>
       </c>
       <c r="T65">
-        <v>2.505461223747295</v>
+        <v>2.575057368851387</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05742751110336558</v>
+        <v>0.05653020624237548</v>
       </c>
       <c r="W65">
-        <v>0.1892685557704442</v>
+        <v>0.189448734586531</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5742751110336557</v>
+        <v>0.5653020624237548</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1976601876285584</v>
+        <v>0.1992101876285584</v>
       </c>
       <c r="C66">
-        <v>0.06503952626661835</v>
+        <v>-0.2492926549272134</v>
       </c>
       <c r="D66">
-        <v>11.36919952626662</v>
+        <v>11.28680734507279</v>
       </c>
       <c r="E66">
-        <v>14.55016</v>
+        <v>14.7821</v>
       </c>
       <c r="F66">
-        <v>14.84416</v>
+        <v>15.0761</v>
       </c>
       <c r="G66">
         <v>3.54</v>
@@ -6693,37 +6693,37 @@
         <v>1.685</v>
       </c>
       <c r="M66">
-        <v>2.980707328</v>
+        <v>3.02728088</v>
       </c>
       <c r="N66">
-        <v>-1.295707328000001</v>
+        <v>-1.342280880000001</v>
       </c>
       <c r="O66">
-        <v>-0.1295707328000001</v>
+        <v>-0.1342280880000001</v>
       </c>
       <c r="P66">
-        <v>-1.166136595200001</v>
+        <v>-1.208052792000001</v>
       </c>
       <c r="Q66">
-        <v>1.3238634048</v>
+        <v>1.281947208</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2122583263699403</v>
+        <v>0.2170142785519386</v>
       </c>
       <c r="T66">
-        <v>2.575057368851387</v>
+        <v>2.648630436532855</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05653020624237548</v>
+        <v>0.05566051076172356</v>
       </c>
       <c r="W66">
-        <v>0.189448734586531</v>
+        <v>0.1896233694390459</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5653020624237548</v>
+        <v>0.5566051076172356</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1992101876285584</v>
+        <v>0.2007601876285584</v>
       </c>
       <c r="C67">
-        <v>-0.2492926549272134</v>
+        <v>-0.5624392417171808</v>
       </c>
       <c r="D67">
-        <v>11.28680734507279</v>
+        <v>11.20560075828282</v>
       </c>
       <c r="E67">
-        <v>14.7821</v>
+        <v>15.01404</v>
       </c>
       <c r="F67">
-        <v>15.0761</v>
+        <v>15.30804</v>
       </c>
       <c r="G67">
         <v>3.54</v>
@@ -6775,37 +6775,37 @@
         <v>1.685</v>
       </c>
       <c r="M67">
-        <v>3.02728088</v>
+        <v>3.073854432</v>
       </c>
       <c r="N67">
-        <v>-1.342280880000001</v>
+        <v>-1.388854432</v>
       </c>
       <c r="O67">
-        <v>-0.1342280880000001</v>
+        <v>-0.1388854432</v>
       </c>
       <c r="P67">
-        <v>-1.208052792000001</v>
+        <v>-1.249968988800001</v>
       </c>
       <c r="Q67">
-        <v>1.281947208</v>
+        <v>1.2400310112</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2170142785519386</v>
+        <v>0.2220499926269956</v>
       </c>
       <c r="T67">
-        <v>2.648630436532855</v>
+        <v>2.726531331724998</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.05566051076172356</v>
+        <v>0.05481716968957623</v>
       </c>
       <c r="W67">
-        <v>0.1896233694390459</v>
+        <v>0.1897927123263331</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5566051076172356</v>
+        <v>0.5481716968957623</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2007601876285584</v>
+        <v>0.2023101876285583</v>
       </c>
       <c r="C68">
-        <v>-0.5624392417171808</v>
+        <v>-0.8744256417273562</v>
       </c>
       <c r="D68">
-        <v>11.20560075828282</v>
+        <v>11.12555435827264</v>
       </c>
       <c r="E68">
-        <v>15.01404</v>
+        <v>15.24598</v>
       </c>
       <c r="F68">
-        <v>15.30804</v>
+        <v>15.53998</v>
       </c>
       <c r="G68">
         <v>3.54</v>
@@ -6857,37 +6857,37 @@
         <v>1.685</v>
       </c>
       <c r="M68">
-        <v>3.073854432</v>
+        <v>3.120427984</v>
       </c>
       <c r="N68">
-        <v>-1.388854432</v>
+        <v>-1.435427984</v>
       </c>
       <c r="O68">
-        <v>-0.1388854432</v>
+        <v>-0.1435427984</v>
       </c>
       <c r="P68">
-        <v>-1.249968988800001</v>
+        <v>-1.2918851856</v>
       </c>
       <c r="Q68">
-        <v>1.2400310112</v>
+        <v>1.1981148144</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2220499926269956</v>
+        <v>0.2273909014944804</v>
       </c>
       <c r="T68">
-        <v>2.726531331724998</v>
+        <v>2.809153493292422</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05481716968957623</v>
+        <v>0.05399900297779151</v>
       </c>
       <c r="W68">
-        <v>0.1897927123263331</v>
+        <v>0.1899570002020595</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5481716968957623</v>
+        <v>0.5399900297779151</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2023101876285583</v>
+        <v>0.2038601876285584</v>
       </c>
       <c r="C69">
-        <v>-0.8744256417273562</v>
+        <v>-1.185276541740999</v>
       </c>
       <c r="D69">
-        <v>11.12555435827264</v>
+        <v>11.046643458259</v>
       </c>
       <c r="E69">
-        <v>15.24598</v>
+        <v>15.47792</v>
       </c>
       <c r="F69">
-        <v>15.53998</v>
+        <v>15.77192</v>
       </c>
       <c r="G69">
         <v>3.54</v>
@@ -6939,37 +6939,37 @@
         <v>1.685</v>
       </c>
       <c r="M69">
-        <v>3.120427984</v>
+        <v>3.167001536</v>
       </c>
       <c r="N69">
-        <v>-1.435427984</v>
+        <v>-1.482001536</v>
       </c>
       <c r="O69">
-        <v>-0.1435427984</v>
+        <v>-0.1482001536</v>
       </c>
       <c r="P69">
-        <v>-1.2918851856</v>
+        <v>-1.3338013824</v>
       </c>
       <c r="Q69">
-        <v>1.1981148144</v>
+        <v>1.1561986176</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2273909014944804</v>
+        <v>0.2330656171661829</v>
       </c>
       <c r="T69">
-        <v>2.809153493292422</v>
+        <v>2.896939539957811</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05399900297779151</v>
+        <v>0.053204899992824</v>
       </c>
       <c r="W69">
-        <v>0.1899570002020595</v>
+        <v>0.190116456081441</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5399900297779151</v>
+        <v>0.5320489999282398</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2038601876285584</v>
+        <v>0.2054101876285583</v>
       </c>
       <c r="C70">
-        <v>-1.185276541740999</v>
+        <v>-1.495015933084225</v>
       </c>
       <c r="D70">
-        <v>11.046643458259</v>
+        <v>10.96884406691577</v>
       </c>
       <c r="E70">
-        <v>15.47792</v>
+        <v>15.70986</v>
       </c>
       <c r="F70">
-        <v>15.77192</v>
+        <v>16.00386</v>
       </c>
       <c r="G70">
         <v>3.54</v>
@@ -7021,37 +7021,37 @@
         <v>1.685</v>
       </c>
       <c r="M70">
-        <v>3.167001536</v>
+        <v>3.213575088</v>
       </c>
       <c r="N70">
-        <v>-1.482001536</v>
+        <v>-1.528575088</v>
       </c>
       <c r="O70">
-        <v>-0.1482001536</v>
+        <v>-0.1528575088</v>
       </c>
       <c r="P70">
-        <v>-1.3338013824</v>
+        <v>-1.3757175792</v>
       </c>
       <c r="Q70">
-        <v>1.1561986176</v>
+        <v>1.1142824208</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2330656171661829</v>
+        <v>0.2391064435263823</v>
       </c>
       <c r="T70">
-        <v>2.896939539957811</v>
+        <v>2.990389202537095</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.053204899992824</v>
+        <v>0.05243381448568162</v>
       </c>
       <c r="W70">
-        <v>0.190116456081441</v>
+        <v>0.1902712900512751</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5320489999282398</v>
+        <v>0.5243381448568162</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2054101876285583</v>
+        <v>0.2069601876285583</v>
       </c>
       <c r="C71">
-        <v>-1.495015933084225</v>
+        <v>-1.803667135944636</v>
       </c>
       <c r="D71">
-        <v>10.96884406691577</v>
+        <v>10.89213286405537</v>
       </c>
       <c r="E71">
-        <v>15.70986</v>
+        <v>15.9418</v>
       </c>
       <c r="F71">
-        <v>16.00386</v>
+        <v>16.2358</v>
       </c>
       <c r="G71">
         <v>3.54</v>
@@ -7103,37 +7103,37 @@
         <v>1.685</v>
       </c>
       <c r="M71">
-        <v>3.213575088</v>
+        <v>3.26014864</v>
       </c>
       <c r="N71">
-        <v>-1.528575088</v>
+        <v>-1.575148640000001</v>
       </c>
       <c r="O71">
-        <v>-0.1528575088</v>
+        <v>-0.1575148640000001</v>
       </c>
       <c r="P71">
-        <v>-1.3757175792</v>
+        <v>-1.417633776</v>
       </c>
       <c r="Q71">
-        <v>1.1142824208</v>
+        <v>1.072366224</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2391064435263823</v>
+        <v>0.2455499916439284</v>
       </c>
       <c r="T71">
-        <v>2.990389202537095</v>
+        <v>3.090068842621664</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05243381448568162</v>
+        <v>0.05168475999302902</v>
       </c>
       <c r="W71">
-        <v>0.1902712900512751</v>
+        <v>0.1904217001933998</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5243381448568162</v>
+        <v>0.5168475999302902</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2069601876285583</v>
+        <v>0.2085101876285583</v>
       </c>
       <c r="C72">
-        <v>-1.803667135944636</v>
+        <v>-2.111252822676505</v>
       </c>
       <c r="D72">
-        <v>10.89213286405537</v>
+        <v>10.8164871773235</v>
       </c>
       <c r="E72">
-        <v>15.9418</v>
+        <v>16.17374</v>
       </c>
       <c r="F72">
-        <v>16.2358</v>
+        <v>16.46774</v>
       </c>
       <c r="G72">
         <v>3.54</v>
@@ -7185,37 +7185,37 @@
         <v>1.685</v>
       </c>
       <c r="M72">
-        <v>3.26014864</v>
+        <v>3.306722192000001</v>
       </c>
       <c r="N72">
-        <v>-1.575148640000001</v>
+        <v>-1.621722192000001</v>
       </c>
       <c r="O72">
-        <v>-0.1575148640000001</v>
+        <v>-0.1621722192000001</v>
       </c>
       <c r="P72">
-        <v>-1.417633776</v>
+        <v>-1.459549972800001</v>
       </c>
       <c r="Q72">
-        <v>1.072366224</v>
+        <v>1.030450027199999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2455499916439284</v>
+        <v>0.2524379223902707</v>
       </c>
       <c r="T72">
-        <v>3.090068842621664</v>
+        <v>3.196622940643102</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.05168475999302902</v>
+        <v>0.05095680562693002</v>
       </c>
       <c r="W72">
-        <v>0.1904217001933998</v>
+        <v>0.1905678734301124</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5168475999302902</v>
+        <v>0.5095680562693001</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2085101876285583</v>
+        <v>0.2100601876285583</v>
       </c>
       <c r="C73">
-        <v>-2.111252822676501</v>
+        <v>-2.41779504014162</v>
       </c>
       <c r="D73">
-        <v>10.8164871773235</v>
+        <v>10.74188495985838</v>
       </c>
       <c r="E73">
-        <v>16.17374</v>
+        <v>16.40568</v>
       </c>
       <c r="F73">
-        <v>16.46774</v>
+        <v>16.69968</v>
       </c>
       <c r="G73">
         <v>3.54</v>
@@ -7267,37 +7267,37 @@
         <v>1.685</v>
       </c>
       <c r="M73">
-        <v>3.306722192</v>
+        <v>3.353295744</v>
       </c>
       <c r="N73">
-        <v>-1.621722192</v>
+        <v>-1.668295744</v>
       </c>
       <c r="O73">
-        <v>-0.1621722192000001</v>
+        <v>-0.1668295744</v>
       </c>
       <c r="P73">
-        <v>-1.4595499728</v>
+        <v>-1.5014661696</v>
       </c>
       <c r="Q73">
-        <v>1.0304500272</v>
+        <v>0.9885338304000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2524379223902707</v>
+        <v>0.2598178481899232</v>
       </c>
       <c r="T73">
-        <v>3.1966229406431</v>
+        <v>3.310788045666068</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.05095680562693002</v>
+        <v>0.05024907221544489</v>
       </c>
       <c r="W73">
-        <v>0.1905678734301124</v>
+        <v>0.1907099862991387</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5095680562693001</v>
+        <v>0.5024907221544488</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2100601876285583</v>
+        <v>0.2374940723737051</v>
       </c>
       <c r="C74">
-        <v>-2.41779504014162</v>
+        <v>-3.818373920124259</v>
       </c>
       <c r="D74">
-        <v>10.74188495985838</v>
+        <v>9.573246079875739</v>
       </c>
       <c r="E74">
-        <v>16.40568</v>
+        <v>16.63762</v>
       </c>
       <c r="F74">
-        <v>16.69968</v>
+        <v>16.93162</v>
       </c>
       <c r="G74">
         <v>3.54</v>
@@ -7349,45 +7349,45 @@
         <v>1.685</v>
       </c>
       <c r="M74">
-        <v>3.353295744</v>
+        <v>3.992475996</v>
       </c>
       <c r="N74">
-        <v>-1.668295744</v>
+        <v>-2.307475996</v>
       </c>
       <c r="O74">
-        <v>-0.1668295744</v>
+        <v>-0.2307475996</v>
       </c>
       <c r="P74">
-        <v>-1.5014661696</v>
+        <v>-2.076728396400001</v>
       </c>
       <c r="Q74">
-        <v>0.9885338304000002</v>
+        <v>0.4132716035999997</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2598178481899232</v>
+        <v>0.2689810453271308</v>
       </c>
       <c r="T74">
-        <v>3.310788045666068</v>
+        <v>3.452539791132767</v>
       </c>
       <c r="U74">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05024907221544489</v>
+        <v>0.04220438649319808</v>
       </c>
       <c r="W74">
-        <v>0.1907099862991387</v>
+        <v>0.2258482056649039</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.5024907221544488</v>
+        <v>0.4220438649319809</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2374940723737051</v>
+        <v>0.2393940723737052</v>
       </c>
       <c r="C75">
-        <v>-3.818373920124259</v>
+        <v>-4.121906058444548</v>
       </c>
       <c r="D75">
-        <v>9.573246079875739</v>
+        <v>9.501653941555453</v>
       </c>
       <c r="E75">
-        <v>16.63762</v>
+        <v>16.86956</v>
       </c>
       <c r="F75">
-        <v>16.93162</v>
+        <v>17.16356</v>
       </c>
       <c r="G75">
         <v>3.54</v>
@@ -7431,37 +7431,37 @@
         <v>1.685</v>
       </c>
       <c r="M75">
-        <v>3.992475996</v>
+        <v>4.047167448000001</v>
       </c>
       <c r="N75">
-        <v>-2.307475996</v>
+        <v>-2.362167448000001</v>
       </c>
       <c r="O75">
-        <v>-0.2307475996</v>
+        <v>-0.2362167448000001</v>
       </c>
       <c r="P75">
-        <v>-2.076728396400001</v>
+        <v>-2.125950703200001</v>
       </c>
       <c r="Q75">
-        <v>0.4132716035999997</v>
+        <v>0.3640492967999993</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2689810453271308</v>
+        <v>0.2775649316858666</v>
       </c>
       <c r="T75">
-        <v>3.452539791132767</v>
+        <v>3.585329783099412</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04220438649319808</v>
+        <v>0.0416340569459927</v>
       </c>
       <c r="W75">
-        <v>0.2258482056649039</v>
+        <v>0.2259826893721349</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4220438649319809</v>
+        <v>0.4163405694599269</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2393940723737052</v>
+        <v>0.2412940723737052</v>
       </c>
       <c r="C76">
-        <v>-4.121906058444548</v>
+        <v>-4.424375362085112</v>
       </c>
       <c r="D76">
-        <v>9.501653941555453</v>
+        <v>9.431124637914886</v>
       </c>
       <c r="E76">
-        <v>16.86956</v>
+        <v>17.1015</v>
       </c>
       <c r="F76">
-        <v>17.16356</v>
+        <v>17.3955</v>
       </c>
       <c r="G76">
         <v>3.54</v>
@@ -7513,37 +7513,37 @@
         <v>1.685</v>
       </c>
       <c r="M76">
-        <v>4.047167448000001</v>
+        <v>4.1018589</v>
       </c>
       <c r="N76">
-        <v>-2.362167448000001</v>
+        <v>-2.4168589</v>
       </c>
       <c r="O76">
-        <v>-0.2362167448000001</v>
+        <v>-0.24168589</v>
       </c>
       <c r="P76">
-        <v>-2.125950703200001</v>
+        <v>-2.17517301</v>
       </c>
       <c r="Q76">
-        <v>0.3640492967999993</v>
+        <v>0.3148269899999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2775649316858666</v>
+        <v>0.2868355289533013</v>
       </c>
       <c r="T76">
-        <v>3.585329783099412</v>
+        <v>3.728742974423389</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0416340569459927</v>
+        <v>0.0410789361867128</v>
       </c>
       <c r="W76">
-        <v>0.2259826893721349</v>
+        <v>0.2261135868471731</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4163405694599269</v>
+        <v>0.410789361867128</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2412940723737052</v>
+        <v>0.2431940723737052</v>
       </c>
       <c r="C77">
-        <v>-4.424375362085112</v>
+        <v>-4.725805324429214</v>
       </c>
       <c r="D77">
-        <v>9.431124637914886</v>
+        <v>9.361634675570786</v>
       </c>
       <c r="E77">
-        <v>17.1015</v>
+        <v>17.33344</v>
       </c>
       <c r="F77">
-        <v>17.3955</v>
+        <v>17.62744</v>
       </c>
       <c r="G77">
         <v>3.54</v>
@@ -7595,37 +7595,37 @@
         <v>1.685</v>
       </c>
       <c r="M77">
-        <v>4.1018589</v>
+        <v>4.156550352</v>
       </c>
       <c r="N77">
-        <v>-2.4168589</v>
+        <v>-2.471550352</v>
       </c>
       <c r="O77">
-        <v>-0.24168589</v>
+        <v>-0.2471550352</v>
       </c>
       <c r="P77">
-        <v>-2.17517301</v>
+        <v>-2.2243953168</v>
       </c>
       <c r="Q77">
-        <v>0.3148269899999998</v>
+        <v>0.2656046831999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2868355289533013</v>
+        <v>0.2968786759930222</v>
       </c>
       <c r="T77">
-        <v>3.728742974423389</v>
+        <v>3.884107265024363</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0410789361867128</v>
+        <v>0.04053842386846658</v>
       </c>
       <c r="W77">
-        <v>0.2261135868471731</v>
+        <v>0.2262410396518156</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.410789361867128</v>
+        <v>0.4053842386846658</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2431940723737052</v>
+        <v>0.2450940723737052</v>
       </c>
       <c r="C78">
-        <v>-4.725805324429214</v>
+        <v>-5.02621875151328</v>
       </c>
       <c r="D78">
-        <v>9.361634675570786</v>
+        <v>9.293161248486719</v>
       </c>
       <c r="E78">
-        <v>17.33344</v>
+        <v>17.56538</v>
       </c>
       <c r="F78">
-        <v>17.62744</v>
+        <v>17.85938</v>
       </c>
       <c r="G78">
         <v>3.54</v>
@@ -7677,37 +7677,37 @@
         <v>1.685</v>
       </c>
       <c r="M78">
-        <v>4.156550352</v>
+        <v>4.211241804</v>
       </c>
       <c r="N78">
-        <v>-2.471550352</v>
+        <v>-2.526241804000001</v>
       </c>
       <c r="O78">
-        <v>-0.2471550352</v>
+        <v>-0.2526241804000001</v>
       </c>
       <c r="P78">
-        <v>-2.2243953168</v>
+        <v>-2.2736176236</v>
       </c>
       <c r="Q78">
-        <v>0.2656046831999999</v>
+        <v>0.2163823763999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2968786759930222</v>
+        <v>0.3077951401666319</v>
       </c>
       <c r="T78">
-        <v>3.884107265024363</v>
+        <v>4.052981493938466</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04053842386846658</v>
+        <v>0.04001195083121377</v>
       </c>
       <c r="W78">
-        <v>0.2262410396518156</v>
+        <v>0.2263651819939998</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4053842386846658</v>
+        <v>0.4001195083121376</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2450940723737052</v>
+        <v>0.2469940723737052</v>
       </c>
       <c r="C79">
-        <v>-5.02621875151328</v>
+        <v>-5.325637786981559</v>
       </c>
       <c r="D79">
-        <v>9.293161248486719</v>
+        <v>9.225682213018441</v>
       </c>
       <c r="E79">
-        <v>17.56538</v>
+        <v>17.79732</v>
       </c>
       <c r="F79">
-        <v>17.85938</v>
+        <v>18.09132</v>
       </c>
       <c r="G79">
         <v>3.54</v>
@@ -7759,37 +7759,37 @@
         <v>1.685</v>
       </c>
       <c r="M79">
-        <v>4.211241804</v>
+        <v>4.265933256</v>
       </c>
       <c r="N79">
-        <v>-2.526241804000001</v>
+        <v>-2.580933256000001</v>
       </c>
       <c r="O79">
-        <v>-0.2526241804000001</v>
+        <v>-0.2580933256000001</v>
       </c>
       <c r="P79">
-        <v>-2.2736176236</v>
+        <v>-2.322839930400001</v>
       </c>
       <c r="Q79">
-        <v>0.2163823763999999</v>
+        <v>0.1671600695999995</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3077951401666319</v>
+        <v>0.3197040101742061</v>
       </c>
       <c r="T79">
-        <v>4.052981493938466</v>
+        <v>4.237207925481124</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04001195083121377</v>
+        <v>0.03949897710260846</v>
       </c>
       <c r="W79">
-        <v>0.2263651819939998</v>
+        <v>0.2264861411992049</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4001195083121376</v>
+        <v>0.3949897710260846</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2469940723737052</v>
+        <v>0.2488940723737052</v>
       </c>
       <c r="C80">
-        <v>-5.325637786981559</v>
+        <v>-5.624083935961394</v>
       </c>
       <c r="D80">
-        <v>9.225682213018441</v>
+        <v>9.159176064038608</v>
       </c>
       <c r="E80">
-        <v>17.79732</v>
+        <v>18.02926</v>
       </c>
       <c r="F80">
-        <v>18.09132</v>
+        <v>18.32326</v>
       </c>
       <c r="G80">
         <v>3.54</v>
@@ -7841,37 +7841,37 @@
         <v>1.685</v>
       </c>
       <c r="M80">
-        <v>4.265933256</v>
+        <v>4.320624708</v>
       </c>
       <c r="N80">
-        <v>-2.580933256000001</v>
+        <v>-2.635624708000001</v>
       </c>
       <c r="O80">
-        <v>-0.2580933256000001</v>
+        <v>-0.2635624708000001</v>
       </c>
       <c r="P80">
-        <v>-2.322839930400001</v>
+        <v>-2.372062237200001</v>
       </c>
       <c r="Q80">
-        <v>0.1671600695999995</v>
+        <v>0.1179377627999996</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3197040101742061</v>
+        <v>0.3327470582777397</v>
       </c>
       <c r="T80">
-        <v>4.237207925481124</v>
+        <v>4.438979731456415</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03949897710260846</v>
+        <v>0.03899899005067671</v>
       </c>
       <c r="W80">
-        <v>0.2264861411992049</v>
+        <v>0.2266040381460504</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3949897710260846</v>
+        <v>0.3899899005067671</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2488940723737052</v>
+        <v>0.2507940723737052</v>
       </c>
       <c r="C81">
-        <v>-5.624083935961394</v>
+        <v>-5.921578087913222</v>
       </c>
       <c r="D81">
-        <v>9.159176064038608</v>
+        <v>9.093621912086778</v>
       </c>
       <c r="E81">
-        <v>18.02926</v>
+        <v>18.2612</v>
       </c>
       <c r="F81">
-        <v>18.32326</v>
+        <v>18.5552</v>
       </c>
       <c r="G81">
         <v>3.54</v>
@@ -7923,37 +7923,37 @@
         <v>1.685</v>
       </c>
       <c r="M81">
-        <v>4.320624708</v>
+        <v>4.37531616</v>
       </c>
       <c r="N81">
-        <v>-2.635624708000001</v>
+        <v>-2.69031616</v>
       </c>
       <c r="O81">
-        <v>-0.2635624708000001</v>
+        <v>-0.269031616</v>
       </c>
       <c r="P81">
-        <v>-2.372062237200001</v>
+        <v>-2.421284544</v>
       </c>
       <c r="Q81">
-        <v>0.1179377627999996</v>
+        <v>0.06871545600000006</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3327470582777397</v>
+        <v>0.3470944111916267</v>
       </c>
       <c r="T81">
-        <v>4.438979731456415</v>
+        <v>4.660928718029236</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03899899005067671</v>
+        <v>0.03851150267504325</v>
       </c>
       <c r="W81">
-        <v>0.2266040381460504</v>
+        <v>0.2267189876692248</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3899899005067671</v>
+        <v>0.3851150267504325</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2507940723737052</v>
+        <v>0.2526940723737052</v>
       </c>
       <c r="C82">
-        <v>-5.921578087913222</v>
+        <v>-6.218140538506312</v>
       </c>
       <c r="D82">
-        <v>9.093621912086778</v>
+        <v>9.028999461493688</v>
       </c>
       <c r="E82">
-        <v>18.2612</v>
+        <v>18.49314</v>
       </c>
       <c r="F82">
-        <v>18.5552</v>
+        <v>18.78714</v>
       </c>
       <c r="G82">
         <v>3.54</v>
@@ -8005,37 +8005,37 @@
         <v>1.685</v>
       </c>
       <c r="M82">
-        <v>4.37531616</v>
+        <v>4.430007612000001</v>
       </c>
       <c r="N82">
-        <v>-2.69031616</v>
+        <v>-2.745007612000001</v>
       </c>
       <c r="O82">
-        <v>-0.269031616</v>
+        <v>-0.2745007612000001</v>
       </c>
       <c r="P82">
-        <v>-2.421284544</v>
+        <v>-2.470506850800001</v>
       </c>
       <c r="Q82">
-        <v>0.06871545600000006</v>
+        <v>0.01949314919999923</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3470944111916267</v>
+        <v>0.3629520117806597</v>
       </c>
       <c r="T82">
-        <v>4.660928718029236</v>
+        <v>4.906240755820249</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03851150267504325</v>
+        <v>0.03803605202473407</v>
       </c>
       <c r="W82">
-        <v>0.2267189876692248</v>
+        <v>0.2268310989325677</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3851150267504325</v>
+        <v>0.3803605202473407</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2526940723737052</v>
+        <v>0.2545940723737052</v>
       </c>
       <c r="C83">
-        <v>-6.218140538506312</v>
+        <v>-6.513791010568305</v>
       </c>
       <c r="D83">
-        <v>9.028999461493688</v>
+        <v>8.965288989431697</v>
       </c>
       <c r="E83">
-        <v>18.49314</v>
+        <v>18.72508</v>
       </c>
       <c r="F83">
-        <v>18.78714</v>
+        <v>19.01908</v>
       </c>
       <c r="G83">
         <v>3.54</v>
@@ -8087,37 +8087,37 @@
         <v>1.685</v>
       </c>
       <c r="M83">
-        <v>4.430007612000001</v>
+        <v>4.484699064000001</v>
       </c>
       <c r="N83">
-        <v>-2.745007612000001</v>
+        <v>-2.799699064000001</v>
       </c>
       <c r="O83">
-        <v>-0.2745007612000001</v>
+        <v>-0.2799699064000001</v>
       </c>
       <c r="P83">
-        <v>-2.470506850800001</v>
+        <v>-2.519729157600001</v>
       </c>
       <c r="Q83">
-        <v>0.01949314919999923</v>
+        <v>-0.02972915760000072</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3629520117806597</v>
+        <v>0.3805715679906964</v>
       </c>
       <c r="T83">
-        <v>4.906240755820249</v>
+        <v>5.178809686699152</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03803605202473407</v>
+        <v>0.03757219773174951</v>
       </c>
       <c r="W83">
-        <v>0.2268310989325677</v>
+        <v>0.2269404757748535</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3803605202473407</v>
+        <v>0.375721977317495</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2545940723737052</v>
+        <v>0.2564940723737053</v>
       </c>
       <c r="C84">
-        <v>-6.513791010568305</v>
+        <v>-6.808548674154054</v>
       </c>
       <c r="D84">
-        <v>8.965288989431697</v>
+        <v>8.902471325845948</v>
       </c>
       <c r="E84">
-        <v>18.72508</v>
+        <v>18.95702</v>
       </c>
       <c r="F84">
-        <v>19.01908</v>
+        <v>19.25102</v>
       </c>
       <c r="G84">
         <v>3.54</v>
@@ -8169,37 +8169,37 @@
         <v>1.685</v>
       </c>
       <c r="M84">
-        <v>4.484699064000001</v>
+        <v>4.539390516</v>
       </c>
       <c r="N84">
-        <v>-2.799699064000001</v>
+        <v>-2.854390516</v>
       </c>
       <c r="O84">
-        <v>-0.2799699064000001</v>
+        <v>-0.2854390516</v>
       </c>
       <c r="P84">
-        <v>-2.519729157600001</v>
+        <v>-2.5689514644</v>
       </c>
       <c r="Q84">
-        <v>-0.02972915760000072</v>
+        <v>-0.07895146440000023</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3805715679906964</v>
+        <v>0.4002640131666197</v>
       </c>
       <c r="T84">
-        <v>5.178809686699152</v>
+        <v>5.483445550622633</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03757219773174951</v>
+        <v>0.0371195206506441</v>
       </c>
       <c r="W84">
-        <v>0.2269404757748535</v>
+        <v>0.2270472170305781</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.375721977317495</v>
+        <v>0.371195206506441</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2564940723737053</v>
+        <v>0.2583940723737052</v>
       </c>
       <c r="C85">
-        <v>-6.808548674154054</v>
+        <v>-7.102432165776609</v>
       </c>
       <c r="D85">
-        <v>8.902471325845948</v>
+        <v>8.840527834223392</v>
       </c>
       <c r="E85">
-        <v>18.95702</v>
+        <v>19.18896</v>
       </c>
       <c r="F85">
-        <v>19.25102</v>
+        <v>19.48296</v>
       </c>
       <c r="G85">
         <v>3.54</v>
@@ -8251,37 +8251,37 @@
         <v>1.685</v>
       </c>
       <c r="M85">
-        <v>4.539390516</v>
+        <v>4.594081968</v>
       </c>
       <c r="N85">
-        <v>-2.854390516</v>
+        <v>-2.909081968000001</v>
       </c>
       <c r="O85">
-        <v>-0.2854390516</v>
+        <v>-0.2909081968000001</v>
       </c>
       <c r="P85">
-        <v>-2.5689514644</v>
+        <v>-2.6181737712</v>
       </c>
       <c r="Q85">
-        <v>-0.07895146440000023</v>
+        <v>-0.1281737712000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4002640131666197</v>
+        <v>0.4224180139895335</v>
       </c>
       <c r="T85">
-        <v>5.483445550622633</v>
+        <v>5.826160897536547</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0371195206506441</v>
+        <v>0.03667762159527928</v>
       </c>
       <c r="W85">
-        <v>0.2270472170305781</v>
+        <v>0.2271514168278332</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.371195206506441</v>
+        <v>0.3667762159527929</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2583940723737052</v>
+        <v>0.2602940723737052</v>
       </c>
       <c r="C86">
-        <v>-7.102432165776605</v>
+        <v>-7.395459606840927</v>
       </c>
       <c r="D86">
-        <v>8.840527834223392</v>
+        <v>8.779440393159074</v>
       </c>
       <c r="E86">
-        <v>19.18896</v>
+        <v>19.4209</v>
       </c>
       <c r="F86">
-        <v>19.48296</v>
+        <v>19.7149</v>
       </c>
       <c r="G86">
         <v>3.54</v>
@@ -8333,37 +8333,37 @@
         <v>1.685</v>
       </c>
       <c r="M86">
-        <v>4.594081968</v>
+        <v>4.64877342</v>
       </c>
       <c r="N86">
-        <v>-2.909081968000001</v>
+        <v>-2.963773420000001</v>
       </c>
       <c r="O86">
-        <v>-0.2909081968000001</v>
+        <v>-0.2963773420000001</v>
       </c>
       <c r="P86">
-        <v>-2.6181737712</v>
+        <v>-2.667396078000001</v>
       </c>
       <c r="Q86">
-        <v>-0.1281737712000002</v>
+        <v>-0.1773960780000006</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4224180139895333</v>
+        <v>0.4475258815888355</v>
       </c>
       <c r="T86">
-        <v>5.826160897536544</v>
+        <v>6.214571624038981</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03667762159527928</v>
+        <v>0.03624612016474659</v>
       </c>
       <c r="W86">
-        <v>0.2271514168278332</v>
+        <v>0.2272531648651528</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3667762159527929</v>
+        <v>0.3624612016474659</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2602940723737052</v>
+        <v>0.2621940723737052</v>
       </c>
       <c r="C87">
-        <v>-7.395459606840927</v>
+        <v>-7.68764862131852</v>
       </c>
       <c r="D87">
-        <v>8.779440393159074</v>
+        <v>8.719191378681478</v>
       </c>
       <c r="E87">
-        <v>19.4209</v>
+        <v>19.65284</v>
       </c>
       <c r="F87">
-        <v>19.7149</v>
+        <v>19.94684</v>
       </c>
       <c r="G87">
         <v>3.54</v>
@@ -8415,37 +8415,37 @@
         <v>1.685</v>
       </c>
       <c r="M87">
-        <v>4.64877342</v>
+        <v>4.703464872</v>
       </c>
       <c r="N87">
-        <v>-2.963773420000001</v>
+        <v>-3.018464872</v>
       </c>
       <c r="O87">
-        <v>-0.2963773420000001</v>
+        <v>-0.3018464872</v>
       </c>
       <c r="P87">
-        <v>-2.667396078000001</v>
+        <v>-2.7166183848</v>
       </c>
       <c r="Q87">
-        <v>-0.1773960780000006</v>
+        <v>-0.2266183847999996</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4475258815888355</v>
+        <v>0.4762205874166094</v>
       </c>
       <c r="T87">
-        <v>6.214571624038981</v>
+        <v>6.658469597184622</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03624612016474659</v>
+        <v>0.03582465365120303</v>
       </c>
       <c r="W87">
-        <v>0.2272531648651528</v>
+        <v>0.2273525466690463</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3624612016474659</v>
+        <v>0.3582465365120303</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2621940723737052</v>
+        <v>0.2640940723737052</v>
       </c>
       <c r="C88">
-        <v>-7.68764862131852</v>
+        <v>-7.979016352699364</v>
       </c>
       <c r="D88">
-        <v>8.719191378681478</v>
+        <v>8.659763647300636</v>
       </c>
       <c r="E88">
-        <v>19.65284</v>
+        <v>19.88478</v>
       </c>
       <c r="F88">
-        <v>19.94684</v>
+        <v>20.17878</v>
       </c>
       <c r="G88">
         <v>3.54</v>
@@ -8497,37 +8497,37 @@
         <v>1.685</v>
       </c>
       <c r="M88">
-        <v>4.703464872</v>
+        <v>4.758156324</v>
       </c>
       <c r="N88">
-        <v>-3.018464872</v>
+        <v>-3.073156324</v>
       </c>
       <c r="O88">
-        <v>-0.3018464872</v>
+        <v>-0.3073156324</v>
       </c>
       <c r="P88">
-        <v>-2.7166183848</v>
+        <v>-2.7658406916</v>
       </c>
       <c r="Q88">
-        <v>-0.2266183847999996</v>
+        <v>-0.2758406916</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4762205874166094</v>
+        <v>0.5093298633717332</v>
       </c>
       <c r="T88">
-        <v>6.658469597184622</v>
+        <v>7.170659566198824</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03582465365120303</v>
+        <v>0.03541287602302828</v>
       </c>
       <c r="W88">
-        <v>0.2273525466690463</v>
+        <v>0.2274496438337699</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3582465365120303</v>
+        <v>0.3541287602302827</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2640940723737052</v>
+        <v>0.2659940723737052</v>
       </c>
       <c r="C89">
-        <v>-7.979016352699364</v>
+        <v>-8.269579480255207</v>
       </c>
       <c r="D89">
-        <v>8.659763647300636</v>
+        <v>8.60114051974479</v>
       </c>
       <c r="E89">
-        <v>19.88478</v>
+        <v>20.11672</v>
       </c>
       <c r="F89">
-        <v>20.17878</v>
+        <v>20.41072</v>
       </c>
       <c r="G89">
         <v>3.54</v>
@@ -8579,37 +8579,37 @@
         <v>1.685</v>
       </c>
       <c r="M89">
-        <v>4.758156324</v>
+        <v>4.812847776</v>
       </c>
       <c r="N89">
-        <v>-3.073156324</v>
+        <v>-3.127847776</v>
       </c>
       <c r="O89">
-        <v>-0.3073156324</v>
+        <v>-0.3127847776000001</v>
       </c>
       <c r="P89">
-        <v>-2.7658406916</v>
+        <v>-2.8150629984</v>
       </c>
       <c r="Q89">
-        <v>-0.2758406916</v>
+        <v>-0.3250629984</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5093298633717332</v>
+        <v>0.5479573519860443</v>
       </c>
       <c r="T89">
-        <v>7.170659566198824</v>
+        <v>7.768214530048726</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03541287602302828</v>
+        <v>0.03501045697731205</v>
       </c>
       <c r="W89">
-        <v>0.2274496438337699</v>
+        <v>0.2275445342447498</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3541287602302827</v>
+        <v>0.3501045697731204</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2659940723737052</v>
+        <v>0.2678940723737052</v>
       </c>
       <c r="C90">
-        <v>-8.269579480255207</v>
+        <v>-8.559354234646804</v>
       </c>
       <c r="D90">
-        <v>8.60114051974479</v>
+        <v>8.543305765353196</v>
       </c>
       <c r="E90">
-        <v>20.11672</v>
+        <v>20.34866</v>
       </c>
       <c r="F90">
-        <v>20.41072</v>
+        <v>20.64266</v>
       </c>
       <c r="G90">
         <v>3.54</v>
@@ -8661,37 +8661,37 @@
         <v>1.685</v>
       </c>
       <c r="M90">
-        <v>4.812847776</v>
+        <v>4.867539228</v>
       </c>
       <c r="N90">
-        <v>-3.127847776</v>
+        <v>-3.182539228</v>
       </c>
       <c r="O90">
-        <v>-0.3127847776000001</v>
+        <v>-0.3182539228000001</v>
       </c>
       <c r="P90">
-        <v>-2.8150629984</v>
+        <v>-2.8642853052</v>
       </c>
       <c r="Q90">
-        <v>-0.3250629984</v>
+        <v>-0.3742853051999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5479573519860443</v>
+        <v>0.5936080203484122</v>
       </c>
       <c r="T90">
-        <v>7.768214530048726</v>
+        <v>8.474415850962249</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03501045697731205</v>
+        <v>0.03461708105621866</v>
       </c>
       <c r="W90">
-        <v>0.2275445342447498</v>
+        <v>0.2276372922869437</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3501045697731204</v>
+        <v>0.3461708105621865</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2678940723737052</v>
+        <v>0.2697940723737052</v>
       </c>
       <c r="C91">
-        <v>-8.559354234646804</v>
+        <v>-8.848356412905627</v>
       </c>
       <c r="D91">
-        <v>8.543305765353196</v>
+        <v>8.486243587094375</v>
       </c>
       <c r="E91">
-        <v>20.34866</v>
+        <v>20.5806</v>
       </c>
       <c r="F91">
-        <v>20.64266</v>
+        <v>20.8746</v>
       </c>
       <c r="G91">
         <v>3.54</v>
@@ -8743,37 +8743,37 @@
         <v>1.685</v>
       </c>
       <c r="M91">
-        <v>4.867539228</v>
+        <v>4.92223068</v>
       </c>
       <c r="N91">
-        <v>-3.182539228</v>
+        <v>-3.237230680000001</v>
       </c>
       <c r="O91">
-        <v>-0.3182539228000001</v>
+        <v>-0.3237230680000001</v>
       </c>
       <c r="P91">
-        <v>-2.8642853052</v>
+        <v>-2.913507612000001</v>
       </c>
       <c r="Q91">
-        <v>-0.3742853051999999</v>
+        <v>-0.4235076120000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5936080203484122</v>
+        <v>0.6483888223832533</v>
       </c>
       <c r="T91">
-        <v>8.474415850962249</v>
+        <v>9.321857436058473</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03461708105621866</v>
+        <v>0.03423244682226067</v>
       </c>
       <c r="W91">
-        <v>0.2276372922869437</v>
+        <v>0.2277279890393109</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3461708105621865</v>
+        <v>0.3423244682226066</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2697940723737052</v>
+        <v>0.2716940723737052</v>
       </c>
       <c r="C92">
-        <v>-8.848356412905627</v>
+        <v>-9.136601392819212</v>
       </c>
       <c r="D92">
-        <v>8.486243587094375</v>
+        <v>8.429938607180786</v>
       </c>
       <c r="E92">
-        <v>20.5806</v>
+        <v>20.81254</v>
       </c>
       <c r="F92">
-        <v>20.8746</v>
+        <v>21.10654</v>
       </c>
       <c r="G92">
         <v>3.54</v>
@@ -8825,37 +8825,37 @@
         <v>1.685</v>
       </c>
       <c r="M92">
-        <v>4.92223068</v>
+        <v>4.976922132</v>
       </c>
       <c r="N92">
-        <v>-3.237230680000001</v>
+        <v>-3.291922132000001</v>
       </c>
       <c r="O92">
-        <v>-0.3237230680000001</v>
+        <v>-0.3291922132000001</v>
       </c>
       <c r="P92">
-        <v>-2.913507612000001</v>
+        <v>-2.9627299188</v>
       </c>
       <c r="Q92">
-        <v>-0.4235076120000003</v>
+        <v>-0.4727299188000003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6483888223832533</v>
+        <v>0.7153431359813927</v>
       </c>
       <c r="T92">
-        <v>9.321857436058473</v>
+        <v>10.3576193733983</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03423244682226067</v>
+        <v>0.03385626608795011</v>
       </c>
       <c r="W92">
-        <v>0.2277279890393109</v>
+        <v>0.2278166924564614</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3423244682226066</v>
+        <v>0.338562660879501</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2716940723737052</v>
+        <v>0.2735940723737052</v>
       </c>
       <c r="C93">
-        <v>-9.136601392819212</v>
+        <v>-9.42410414674762</v>
       </c>
       <c r="D93">
-        <v>8.429938607180786</v>
+        <v>8.37437585325238</v>
       </c>
       <c r="E93">
-        <v>20.81254</v>
+        <v>21.04448</v>
       </c>
       <c r="F93">
-        <v>21.10654</v>
+        <v>21.33848</v>
       </c>
       <c r="G93">
         <v>3.54</v>
@@ -8907,37 +8907,37 @@
         <v>1.685</v>
       </c>
       <c r="M93">
-        <v>4.976922132</v>
+        <v>5.031613584</v>
       </c>
       <c r="N93">
-        <v>-3.291922132000001</v>
+        <v>-3.346613584000001</v>
       </c>
       <c r="O93">
-        <v>-0.3291922132000001</v>
+        <v>-0.3346613584000001</v>
       </c>
       <c r="P93">
-        <v>-2.9627299188</v>
+        <v>-3.011952225600001</v>
       </c>
       <c r="Q93">
-        <v>-0.4727299188000003</v>
+        <v>-0.5219522256000007</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7153431359813927</v>
+        <v>0.799036027979067</v>
       </c>
       <c r="T93">
-        <v>10.3576193733983</v>
+        <v>11.6523217950731</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03385626608795011</v>
+        <v>0.03348826319568978</v>
       </c>
       <c r="W93">
-        <v>0.2278166924564614</v>
+        <v>0.2279034675384564</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.338562660879501</v>
+        <v>0.3348826319568978</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2735940723737052</v>
+        <v>0.2754940723737052</v>
       </c>
       <c r="C94">
-        <v>-9.42410414674762</v>
+        <v>-9.710879254897009</v>
       </c>
       <c r="D94">
-        <v>8.37437585325238</v>
+        <v>8.319540745102991</v>
       </c>
       <c r="E94">
-        <v>21.04448</v>
+        <v>21.27642</v>
       </c>
       <c r="F94">
-        <v>21.33848</v>
+        <v>21.57042</v>
       </c>
       <c r="G94">
         <v>3.54</v>
@@ -8989,37 +8989,37 @@
         <v>1.685</v>
       </c>
       <c r="M94">
-        <v>5.031613584</v>
+        <v>5.086305036</v>
       </c>
       <c r="N94">
-        <v>-3.346613584000001</v>
+        <v>-3.401305036</v>
       </c>
       <c r="O94">
-        <v>-0.3346613584000001</v>
+        <v>-0.3401305036</v>
       </c>
       <c r="P94">
-        <v>-3.011952225600001</v>
+        <v>-3.0611745324</v>
       </c>
       <c r="Q94">
-        <v>-0.5219522256000007</v>
+        <v>-0.5711745323999997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.799036027979067</v>
+        <v>0.9066411748332196</v>
       </c>
       <c r="T94">
-        <v>11.6523217950731</v>
+        <v>13.31693919436925</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03348826319568978</v>
+        <v>0.03312817434412323</v>
       </c>
       <c r="W94">
-        <v>0.2279034675384564</v>
+        <v>0.2279883764896558</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3348826319568978</v>
+        <v>0.3312817434412323</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2754940723737052</v>
+        <v>0.2773940723737052</v>
       </c>
       <c r="C95">
-        <v>-9.710879254897009</v>
+        <v>-9.996940918075214</v>
       </c>
       <c r="D95">
-        <v>8.319540745102991</v>
+        <v>8.265419081924787</v>
       </c>
       <c r="E95">
-        <v>21.27642</v>
+        <v>21.50836</v>
       </c>
       <c r="F95">
-        <v>21.57042</v>
+        <v>21.80236</v>
       </c>
       <c r="G95">
         <v>3.54</v>
@@ -9071,37 +9071,37 @@
         <v>1.685</v>
       </c>
       <c r="M95">
-        <v>5.086305036</v>
+        <v>5.140996488</v>
       </c>
       <c r="N95">
-        <v>-3.401305036</v>
+        <v>-3.455996488</v>
       </c>
       <c r="O95">
-        <v>-0.3401305036</v>
+        <v>-0.3455996488</v>
       </c>
       <c r="P95">
-        <v>-3.0611745324</v>
+        <v>-3.1103968392</v>
       </c>
       <c r="Q95">
-        <v>-0.5711745323999997</v>
+        <v>-0.6203968392000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9066411748332196</v>
+        <v>1.05011470397209</v>
       </c>
       <c r="T95">
-        <v>13.31693919436925</v>
+        <v>15.53642906009747</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03312817434412323</v>
+        <v>0.03277574695748362</v>
       </c>
       <c r="W95">
-        <v>0.2279883764896558</v>
+        <v>0.2280714788674254</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3312817434412323</v>
+        <v>0.3277574695748362</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2773940723737052</v>
+        <v>0.2792940723737052</v>
       </c>
       <c r="C96">
-        <v>-9.996940918075214</v>
+        <v>-10.28230296995256</v>
       </c>
       <c r="D96">
-        <v>8.265419081924787</v>
+        <v>8.211997030047437</v>
       </c>
       <c r="E96">
-        <v>21.50836</v>
+        <v>21.7403</v>
       </c>
       <c r="F96">
-        <v>21.80236</v>
+        <v>22.0343</v>
       </c>
       <c r="G96">
         <v>3.54</v>
@@ -9153,37 +9153,37 @@
         <v>1.685</v>
       </c>
       <c r="M96">
-        <v>5.140996488</v>
+        <v>5.195687940000001</v>
       </c>
       <c r="N96">
-        <v>-3.455996488</v>
+        <v>-3.510687940000001</v>
       </c>
       <c r="O96">
-        <v>-0.3455996488</v>
+        <v>-0.3510687940000001</v>
       </c>
       <c r="P96">
-        <v>-3.1103968392</v>
+        <v>-3.159619146000001</v>
       </c>
       <c r="Q96">
-        <v>-0.6203968392000001</v>
+        <v>-0.6696191460000009</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.05011470397209</v>
+        <v>1.250977644766508</v>
       </c>
       <c r="T96">
-        <v>15.53642906009747</v>
+        <v>18.64371487211697</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03277574695748362</v>
+        <v>0.03243073909477326</v>
       </c>
       <c r="W96">
-        <v>0.2280714788674254</v>
+        <v>0.2281528317214525</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3277574695748362</v>
+        <v>0.3243073909477325</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2792940723737052</v>
+        <v>0.2811940723737052</v>
       </c>
       <c r="C97">
-        <v>-10.28230296995256</v>
+        <v>-10.56697888885036</v>
       </c>
       <c r="D97">
-        <v>8.211997030047437</v>
+        <v>8.15926111114964</v>
       </c>
       <c r="E97">
-        <v>21.7403</v>
+        <v>21.97224</v>
       </c>
       <c r="F97">
-        <v>22.0343</v>
+        <v>22.26624</v>
       </c>
       <c r="G97">
         <v>3.54</v>
@@ -9235,37 +9235,37 @@
         <v>1.685</v>
       </c>
       <c r="M97">
-        <v>5.195687940000001</v>
+        <v>5.250379392</v>
       </c>
       <c r="N97">
-        <v>-3.510687940000001</v>
+        <v>-3.565379392000001</v>
       </c>
       <c r="O97">
-        <v>-0.3510687940000001</v>
+        <v>-0.3565379392000001</v>
       </c>
       <c r="P97">
-        <v>-3.159619146000001</v>
+        <v>-3.208841452800001</v>
       </c>
       <c r="Q97">
-        <v>-0.6696191460000009</v>
+        <v>-0.7188414528000004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.250977644766508</v>
+        <v>1.552272055958136</v>
       </c>
       <c r="T97">
-        <v>18.64371487211697</v>
+        <v>23.30464359014622</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03243073909477326</v>
+        <v>0.03209291889586938</v>
       </c>
       <c r="W97">
-        <v>0.2281528317214525</v>
+        <v>0.228232489724354</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3243073909477325</v>
+        <v>0.3209291889586937</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2811940723737052</v>
+        <v>0.2830940723737052</v>
       </c>
       <c r="C98">
-        <v>-10.56697888885036</v>
+        <v>-10.85098180907798</v>
       </c>
       <c r="D98">
-        <v>8.15926111114964</v>
+        <v>8.107198190922016</v>
       </c>
       <c r="E98">
-        <v>21.97224</v>
+        <v>22.20418</v>
       </c>
       <c r="F98">
-        <v>22.26624</v>
+        <v>22.49818</v>
       </c>
       <c r="G98">
         <v>3.54</v>
@@ -9317,37 +9317,37 @@
         <v>1.685</v>
       </c>
       <c r="M98">
-        <v>5.250379392</v>
+        <v>5.305070843999999</v>
       </c>
       <c r="N98">
-        <v>-3.565379392000001</v>
+        <v>-3.620070844</v>
       </c>
       <c r="O98">
-        <v>-0.3565379392000001</v>
+        <v>-0.3620070844</v>
       </c>
       <c r="P98">
-        <v>-3.208841452800001</v>
+        <v>-3.2580637596</v>
       </c>
       <c r="Q98">
-        <v>-0.7188414528000004</v>
+        <v>-0.7680637595999995</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.552272055958132</v>
+        <v>2.054429407944176</v>
       </c>
       <c r="T98">
-        <v>23.30464359014616</v>
+        <v>31.07285812019488</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03209291889586938</v>
+        <v>0.03176206406189135</v>
       </c>
       <c r="W98">
-        <v>0.228232489724354</v>
+        <v>0.228310505294206</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3209291889586937</v>
+        <v>0.3176206406189135</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2830940723737052</v>
+        <v>0.2849940723737052</v>
       </c>
       <c r="C99">
-        <v>-10.85098180907798</v>
+        <v>-11.13432453183872</v>
       </c>
       <c r="D99">
-        <v>8.107198190922016</v>
+        <v>8.055795468161277</v>
       </c>
       <c r="E99">
-        <v>22.20418</v>
+        <v>22.43612</v>
       </c>
       <c r="F99">
-        <v>22.49818</v>
+        <v>22.73012</v>
       </c>
       <c r="G99">
         <v>3.54</v>
@@ -9399,37 +9399,37 @@
         <v>1.685</v>
       </c>
       <c r="M99">
-        <v>5.305070843999999</v>
+        <v>5.359762296</v>
       </c>
       <c r="N99">
-        <v>-3.620070844</v>
+        <v>-3.674762296000001</v>
       </c>
       <c r="O99">
-        <v>-0.3620070844</v>
+        <v>-0.3674762296000001</v>
       </c>
       <c r="P99">
-        <v>-3.2580637596</v>
+        <v>-3.307286066400001</v>
       </c>
       <c r="Q99">
-        <v>-0.7680637595999995</v>
+        <v>-0.8172860664000003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.054429407944176</v>
+        <v>3.058744111916264</v>
       </c>
       <c r="T99">
-        <v>31.07285812019488</v>
+        <v>46.60928718029232</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03176206406189135</v>
+        <v>0.03143796136738224</v>
       </c>
       <c r="W99">
-        <v>0.228310505294206</v>
+        <v>0.2283869287095713</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3176206406189135</v>
+        <v>0.3143796136738224</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2849940723737052</v>
+        <v>0.2868940723737052</v>
       </c>
       <c r="C100">
-        <v>-11.13432453183872</v>
+        <v>-11.41701953572335</v>
       </c>
       <c r="D100">
-        <v>8.055795468161277</v>
+        <v>8.005040464276645</v>
       </c>
       <c r="E100">
-        <v>22.43612</v>
+        <v>22.66806</v>
       </c>
       <c r="F100">
-        <v>22.73012</v>
+        <v>22.96206</v>
       </c>
       <c r="G100">
         <v>3.54</v>
@@ -9481,37 +9481,37 @@
         <v>1.685</v>
       </c>
       <c r="M100">
-        <v>5.359762296</v>
+        <v>5.414453748</v>
       </c>
       <c r="N100">
-        <v>-3.674762296000001</v>
+        <v>-3.729453748</v>
       </c>
       <c r="O100">
-        <v>-0.3674762296000001</v>
+        <v>-0.3729453748</v>
       </c>
       <c r="P100">
-        <v>-3.307286066400001</v>
+        <v>-3.3565083732</v>
       </c>
       <c r="Q100">
-        <v>-0.8172860664000003</v>
+        <v>-0.8665083731999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.058744111916264</v>
+        <v>6.071688223832528</v>
       </c>
       <c r="T100">
-        <v>46.60928718029232</v>
+        <v>93.21857436058464</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03143796136738224</v>
+        <v>0.03112040620205515</v>
       </c>
       <c r="W100">
-        <v>0.2283869287095713</v>
+        <v>0.2284618082175554</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3143796136738224</v>
+        <v>0.3112040620205515</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2868940723737052</v>
-      </c>
-      <c r="C101">
-        <v>-11.41701953572335</v>
-      </c>
-      <c r="D101">
-        <v>8.005040464276645</v>
-      </c>
-      <c r="E101">
-        <v>22.66806</v>
-      </c>
-      <c r="F101">
-        <v>22.96206</v>
-      </c>
-      <c r="G101">
-        <v>3.54</v>
-      </c>
-      <c r="H101">
-        <v>22.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.175</v>
-      </c>
-      <c r="K101">
-        <v>2.49</v>
-      </c>
-      <c r="L101">
-        <v>1.685</v>
-      </c>
-      <c r="M101">
-        <v>5.414453748</v>
-      </c>
-      <c r="N101">
-        <v>-3.729453748</v>
-      </c>
-      <c r="O101">
-        <v>-0.3729453748</v>
-      </c>
-      <c r="P101">
-        <v>-3.3565083732</v>
-      </c>
-      <c r="Q101">
-        <v>-0.8665083731999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.071688223832528</v>
-      </c>
-      <c r="T101">
-        <v>93.21857436058464</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03112040620205515</v>
-      </c>
-      <c r="W101">
-        <v>0.2284618082175554</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3112040620205515</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
